--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-22).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-22).xlsx
@@ -912,69 +912,69 @@
   </si>
   <si>
     <t>214
-140</t>
-  </si>
-  <si>
-    <t>64</t>
-  </si>
-  <si>
-    <t>R$ 744.395,59</t>
-  </si>
-  <si>
-    <t>R$ 4.962,64
-R$ 5.091,21</t>
-  </si>
-  <si>
-    <t>(9.1%)
-(6.7%)</t>
-  </si>
-  <si>
-    <t>52.4</t>
-  </si>
-  <si>
-    <t>(11.7%)</t>
-  </si>
-  <si>
-    <t>(339.1%)</t>
-  </si>
-  <si>
-    <t>(381.9%)</t>
-  </si>
-  <si>
-    <t>3.2%</t>
-  </si>
-  <si>
-    <t>0.1%</t>
+170</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>R$ 903.004,18</t>
+  </si>
+  <si>
+    <t>R$ 4.988,97
+R$ 5.117,74</t>
+  </si>
+  <si>
+    <t>(9.4%)
+(7.0%)</t>
+  </si>
+  <si>
+    <t>52.6</t>
+  </si>
+  <si>
+    <t>(12.6%)</t>
+  </si>
+  <si>
+    <t>(267.0%)</t>
+  </si>
+  <si>
+    <t>(314.4%)</t>
+  </si>
+  <si>
+    <t>3.6%</t>
+  </si>
+  <si>
+    <t>0.6%</t>
   </si>
   <si>
     <t>26.4</t>
   </si>
   <si>
-    <t>78.2%</t>
-  </si>
-  <si>
-    <t>8.3%</t>
+    <t>76.1%</t>
+  </si>
+  <si>
+    <t>8.2%</t>
   </si>
   <si>
     <t>5.3</t>
   </si>
   <si>
-    <t>6.1</t>
-  </si>
-  <si>
-    <t>11.5</t>
-  </si>
-  <si>
-    <t>18.1</t>
-  </si>
-  <si>
-    <t>74.4%</t>
-  </si>
-  <si>
-    <t>-R$ 23.465,03</t>
-  </si>
-  <si>
-    <t>2.94</t>
+    <t>6.2</t>
+  </si>
+  <si>
+    <t>11.7</t>
+  </si>
+  <si>
+    <t>18.2</t>
+  </si>
+  <si>
+    <t>74.1%</t>
+  </si>
+  <si>
+    <t>-R$ 28.231,75</t>
+  </si>
+  <si>
+    <t>2.95</t>
   </si>
   <si>
     <t>3.52</t>
@@ -1937,7 +1937,7 @@
         <v>19506</v>
       </c>
       <c r="B5" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C5" s="4">
         <v>44</v>
@@ -1973,25 +1973,61 @@
       <c t="s" r="N5" s="4">
         <v>52</v>
       </c>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="6"/>
-      <c r="R5" s="7"/>
-      <c r="S5" s="6"/>
-      <c r="T5" s="6"/>
-      <c r="U5" s="6"/>
-      <c r="V5" s="6"/>
-      <c r="W5" s="6"/>
-      <c r="X5" s="8"/>
-      <c r="Y5" s="6"/>
-      <c r="Z5" s="6"/>
-      <c r="AA5" s="8"/>
-      <c r="AB5" s="8"/>
-      <c r="AC5" s="8"/>
-      <c r="AD5" s="8"/>
-      <c r="AE5" s="6"/>
+      <c r="O5" s="5">
+        <v>7831.6999999999998</v>
+      </c>
+      <c r="P5" s="5">
+        <v>7831.6999999999998</v>
+      </c>
+      <c r="Q5" s="6">
+        <v>-0.1324965163394205</v>
+      </c>
+      <c r="R5" s="7">
+        <v>80</v>
+      </c>
+      <c r="S5" s="6">
+        <v>-0.17525773195876293</v>
+      </c>
+      <c r="T5" s="6">
+        <v>0.34231288226055645</v>
+      </c>
+      <c r="U5" s="6">
+        <v>-0.012657303012117422</v>
+      </c>
+      <c r="V5" s="6">
+        <v>0.034123561934190534</v>
+      </c>
+      <c r="W5" s="6">
+        <v>0.017572876897736123</v>
+      </c>
+      <c r="X5" s="8">
+        <v>28.910456862745097</v>
+      </c>
+      <c r="Y5" s="6">
+        <v>0.56862745098039214</v>
+      </c>
+      <c r="Z5" s="6">
+        <v>0.078431372549019607</v>
+      </c>
+      <c r="AA5" s="8">
+        <v>5.1870129870129871</v>
+      </c>
+      <c r="AB5" s="8">
+        <v>7.965358823529411</v>
+      </c>
+      <c r="AC5" s="8">
+        <v>13.253266999999999</v>
+      </c>
+      <c r="AD5" s="8">
+        <v>19.188562745098039</v>
+      </c>
+      <c r="AE5" s="6">
+        <v>0.60784313725490191</v>
+      </c>
       <c r="AF5" s="9"/>
-      <c r="AG5" s="5"/>
+      <c r="AG5" s="5">
+        <v>-260.69999999999999</v>
+      </c>
       <c r="AH5" s="10">
         <v>2</v>
       </c>
@@ -2125,7 +2161,7 @@
         <v>19508</v>
       </c>
       <c r="B7" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C7" s="4">
         <v>44</v>
@@ -2161,25 +2197,61 @@
       <c t="s" r="N7" s="4">
         <v>52</v>
       </c>
-      <c r="O7" s="5"/>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="7"/>
-      <c r="S7" s="6"/>
-      <c r="T7" s="6"/>
-      <c r="U7" s="6"/>
-      <c r="V7" s="6"/>
-      <c r="W7" s="6"/>
-      <c r="X7" s="8"/>
-      <c r="Y7" s="6"/>
-      <c r="Z7" s="6"/>
-      <c r="AA7" s="8"/>
-      <c r="AB7" s="8"/>
-      <c r="AC7" s="8"/>
-      <c r="AD7" s="8"/>
-      <c r="AE7" s="6"/>
+      <c r="O7" s="5">
+        <v>8005.8900000000003</v>
+      </c>
+      <c r="P7" s="5">
+        <v>8005.8900000000003</v>
+      </c>
+      <c r="Q7" s="6">
+        <v>0.19390393758090196</v>
+      </c>
+      <c r="R7" s="7">
+        <v>75</v>
+      </c>
+      <c r="S7" s="6">
+        <v>-0.1071428571428571</v>
+      </c>
+      <c r="T7" s="6">
+        <v>0.37649454339242727</v>
+      </c>
+      <c r="U7" s="6">
+        <v>-0.0070780512847416089</v>
+      </c>
+      <c r="V7" s="6">
+        <v>0.077634404169929894</v>
+      </c>
+      <c r="W7" s="6">
+        <v>0.043178522312947089</v>
+      </c>
+      <c r="X7" s="8">
+        <v>26.494790625</v>
+      </c>
+      <c r="Y7" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="6">
+        <v>0.09375</v>
+      </c>
+      <c r="AA7" s="8">
+        <v>10.6356765625</v>
+      </c>
+      <c r="AB7" s="8">
+        <v>2.7781250000000002</v>
+      </c>
+      <c r="AC7" s="8">
+        <v>11.723958</v>
+      </c>
+      <c r="AD7" s="8">
+        <v>18.666146874999999</v>
+      </c>
+      <c r="AE7" s="6">
+        <v>0.84375</v>
+      </c>
       <c r="AF7" s="9"/>
-      <c r="AG7" s="5"/>
+      <c r="AG7" s="5">
+        <v>0</v>
+      </c>
       <c r="AH7" s="10">
         <v>5</v>
       </c>
@@ -2353,7 +2425,7 @@
         <v>19511</v>
       </c>
       <c r="B9" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C9" s="4">
         <v>44</v>
@@ -2389,25 +2461,61 @@
       <c t="s" r="N9" s="4">
         <v>52</v>
       </c>
-      <c r="O9" s="5"/>
-      <c r="P9" s="5"/>
-      <c r="Q9" s="6"/>
-      <c r="R9" s="7"/>
-      <c r="S9" s="6"/>
-      <c r="T9" s="6"/>
-      <c r="U9" s="6"/>
-      <c r="V9" s="6"/>
-      <c r="W9" s="6"/>
-      <c r="X9" s="8"/>
-      <c r="Y9" s="6"/>
-      <c r="Z9" s="6"/>
-      <c r="AA9" s="8"/>
-      <c r="AB9" s="8"/>
-      <c r="AC9" s="8"/>
-      <c r="AD9" s="8"/>
-      <c r="AE9" s="6"/>
+      <c r="O9" s="5">
+        <v>6809.8100000000004</v>
+      </c>
+      <c r="P9" s="5">
+        <v>6809.8100000000004</v>
+      </c>
+      <c r="Q9" s="6">
+        <v>-0.19126374207125385</v>
+      </c>
+      <c r="R9" s="7">
+        <v>63</v>
+      </c>
+      <c r="S9" s="6">
+        <v>-0.32258064516129037</v>
+      </c>
+      <c r="T9" s="6">
+        <v>0.35614945204051213</v>
+      </c>
+      <c r="U9" s="6">
+        <v>-0.013526060198449001</v>
+      </c>
+      <c r="V9" s="6">
+        <v>0.04312957336548303</v>
+      </c>
+      <c r="W9" s="6">
+        <v>0.0029977635205681217</v>
+      </c>
+      <c r="X9" s="8">
+        <v>20.194840476190478</v>
+      </c>
+      <c r="Y9" s="6">
+        <v>0.80952380952380953</v>
+      </c>
+      <c r="Z9" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="8">
+        <v>4.0827951612903224</v>
+      </c>
+      <c r="AB9" s="8">
+        <v>4.1743902439024394</v>
+      </c>
+      <c r="AC9" s="8">
+        <v>8.4652630000000002</v>
+      </c>
+      <c r="AD9" s="8">
+        <v>14.398809523809524</v>
+      </c>
+      <c r="AE9" s="6">
+        <v>0.97619047619047616</v>
+      </c>
       <c r="AF9" s="9"/>
-      <c r="AG9" s="5"/>
+      <c r="AG9" s="5">
+        <v>-89.400000000000006</v>
+      </c>
       <c r="AH9" s="10">
         <v>4</v>
       </c>
@@ -2577,7 +2685,7 @@
         <v>19513</v>
       </c>
       <c r="B11" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C11" s="4">
         <v>44</v>
@@ -2613,25 +2721,61 @@
       <c t="s" r="N11" s="4">
         <v>52</v>
       </c>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="6"/>
-      <c r="R11" s="7"/>
-      <c r="S11" s="6"/>
-      <c r="T11" s="6"/>
-      <c r="U11" s="6"/>
-      <c r="V11" s="6"/>
-      <c r="W11" s="6"/>
-      <c r="X11" s="8"/>
-      <c r="Y11" s="6"/>
-      <c r="Z11" s="6"/>
-      <c r="AA11" s="8"/>
-      <c r="AB11" s="8"/>
-      <c r="AC11" s="8"/>
-      <c r="AD11" s="8"/>
-      <c r="AE11" s="6"/>
+      <c r="O11" s="5">
+        <v>10858.040000000001</v>
+      </c>
+      <c r="P11" s="5">
+        <v>10858.040000000001</v>
+      </c>
+      <c r="Q11" s="6">
+        <v>0.15499022442341137</v>
+      </c>
+      <c r="R11" s="7">
+        <v>84</v>
+      </c>
+      <c r="S11" s="6">
+        <v>-0.096774193548387122</v>
+      </c>
+      <c r="T11" s="6">
+        <v>2.8404326195151239</v>
+      </c>
+      <c r="U11" s="6">
+        <v>-0.46450270951295075</v>
+      </c>
+      <c r="V11" s="6">
+        <v>0.034956354922251159</v>
+      </c>
+      <c r="W11" s="6">
+        <v>0.010777037107986338</v>
+      </c>
+      <c r="X11" s="8">
+        <v>23.980512307692308</v>
+      </c>
+      <c r="Y11" s="6">
+        <v>0.38461538461538464</v>
+      </c>
+      <c r="Z11" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="8">
+        <v>6.0252941176470589</v>
+      </c>
+      <c r="AB11" s="8">
+        <v>3.8396825396825398</v>
+      </c>
+      <c r="AC11" s="8">
+        <v>10.04852</v>
+      </c>
+      <c r="AD11" s="8">
+        <v>15.731026153846154</v>
+      </c>
+      <c r="AE11" s="6">
+        <v>0.81538461538461537</v>
+      </c>
       <c r="AF11" s="9"/>
-      <c r="AG11" s="5"/>
+      <c r="AG11" s="5">
+        <v>0</v>
+      </c>
       <c r="AH11" s="10">
         <v>3</v>
       </c>
@@ -2950,10 +3094,10 @@
         <v>0.046875</v>
       </c>
       <c r="T14" s="6">
-        <v>0.33404385182815904</v>
+        <v>0.34477171701017528</v>
       </c>
       <c r="U14" s="6">
-        <v>-0.037330915778741779</v>
+        <v>-0.026603050596725505</v>
       </c>
       <c r="V14" s="6">
         <v>0.0295653199528217</v>
@@ -4077,7 +4221,7 @@
         <v>19529</v>
       </c>
       <c r="B23" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C23" s="4">
         <v>44</v>
@@ -4113,25 +4257,61 @@
       <c t="s" r="N23" s="4">
         <v>52</v>
       </c>
-      <c r="O23" s="5"/>
-      <c r="P23" s="5"/>
-      <c r="Q23" s="6"/>
-      <c r="R23" s="7"/>
-      <c r="S23" s="6"/>
-      <c r="T23" s="6"/>
-      <c r="U23" s="6"/>
-      <c r="V23" s="6"/>
-      <c r="W23" s="6"/>
-      <c r="X23" s="8"/>
-      <c r="Y23" s="6"/>
-      <c r="Z23" s="6"/>
-      <c r="AA23" s="8"/>
-      <c r="AB23" s="8"/>
-      <c r="AC23" s="8"/>
-      <c r="AD23" s="8"/>
-      <c r="AE23" s="6"/>
+      <c r="O23" s="5">
+        <v>10102.25</v>
+      </c>
+      <c r="P23" s="5">
+        <v>10102.25</v>
+      </c>
+      <c r="Q23" s="6">
+        <v>-0.014318470094643376</v>
+      </c>
+      <c r="R23" s="7">
+        <v>107</v>
+      </c>
+      <c r="S23" s="6">
+        <v>-0.061403508771929793</v>
+      </c>
+      <c r="T23" s="6">
+        <v>0.34356845257244673</v>
+      </c>
+      <c r="U23" s="6">
+        <v>-0.01621080452374471</v>
+      </c>
+      <c r="V23" s="6">
+        <v>0.027184934049345445</v>
+      </c>
+      <c r="W23" s="6">
+        <v>0.011327080600856245</v>
+      </c>
+      <c r="X23" s="8">
+        <v>28.61187260273973</v>
+      </c>
+      <c r="Y23" s="6">
+        <v>0.80821917808219179</v>
+      </c>
+      <c r="Z23" s="6">
+        <v>0.082191780821917804</v>
+      </c>
+      <c r="AA23" s="8">
+        <v>7.2909523809523806</v>
+      </c>
+      <c r="AB23" s="8">
+        <v>4.4726847222222226</v>
+      </c>
+      <c r="AC23" s="8">
+        <v>12.302821</v>
+      </c>
+      <c r="AD23" s="8">
+        <v>19.160273972602742</v>
+      </c>
+      <c r="AE23" s="6">
+        <v>0.61643835616438358</v>
+      </c>
       <c r="AF23" s="9"/>
-      <c r="AG23" s="5"/>
+      <c r="AG23" s="5">
+        <v>-89.430000000000007</v>
+      </c>
       <c r="AH23" s="10">
         <v>2</v>
       </c>
@@ -4529,7 +4709,7 @@
         <v>19545</v>
       </c>
       <c r="B27" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C27" s="4">
         <v>44</v>
@@ -4565,25 +4745,61 @@
       <c t="s" r="N27" s="4">
         <v>52</v>
       </c>
-      <c r="O27" s="5"/>
-      <c r="P27" s="5"/>
-      <c r="Q27" s="6"/>
-      <c r="R27" s="7"/>
-      <c r="S27" s="6"/>
-      <c r="T27" s="6"/>
-      <c r="U27" s="6"/>
-      <c r="V27" s="6"/>
-      <c r="W27" s="6"/>
-      <c r="X27" s="8"/>
-      <c r="Y27" s="6"/>
-      <c r="Z27" s="6"/>
-      <c r="AA27" s="8"/>
-      <c r="AB27" s="8"/>
-      <c r="AC27" s="8"/>
-      <c r="AD27" s="8"/>
-      <c r="AE27" s="6"/>
+      <c r="O27" s="5">
+        <v>4991.9499999999998</v>
+      </c>
+      <c r="P27" s="5">
+        <v>4991.9499999999998</v>
+      </c>
+      <c r="Q27" s="6">
+        <v>-0.31285126907675853</v>
+      </c>
+      <c r="R27" s="7">
+        <v>52</v>
+      </c>
+      <c r="S27" s="6">
+        <v>-0.31578947368421051</v>
+      </c>
+      <c r="T27" s="6">
+        <v>0.28561962760043669</v>
+      </c>
+      <c r="U27" s="6">
+        <v>-0.047242280070914175</v>
+      </c>
+      <c r="V27" s="6">
+        <v>0.062615410811406369</v>
+      </c>
+      <c r="W27" s="6">
+        <v>0.053066036318472745</v>
+      </c>
+      <c r="X27" s="8">
+        <v>25.504024137931037</v>
+      </c>
+      <c r="Y27" s="6">
+        <v>0.48275862068965519</v>
+      </c>
+      <c r="Z27" s="6">
+        <v>0.034482758620689655</v>
+      </c>
+      <c r="AA27" s="8">
+        <v>5.0342773584905665</v>
+      </c>
+      <c r="AB27" s="8">
+        <v>5.9005964285714283</v>
+      </c>
+      <c r="AC27" s="8">
+        <v>10.864388</v>
+      </c>
+      <c r="AD27" s="8">
+        <v>18.509196551724138</v>
+      </c>
+      <c r="AE27" s="6">
+        <v>0.72413793103448276</v>
+      </c>
       <c r="AF27" s="9"/>
-      <c r="AG27" s="5"/>
+      <c r="AG27" s="5">
+        <v>0</v>
+      </c>
       <c r="AH27" s="10">
         <v>2</v>
       </c>
@@ -5539,7 +5755,7 @@
         <v>19561</v>
       </c>
       <c r="B35" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C35" s="4">
         <v>44</v>
@@ -5575,25 +5791,61 @@
       <c t="s" r="N35" s="4">
         <v>52</v>
       </c>
-      <c r="O35" s="5"/>
-      <c r="P35" s="5"/>
-      <c r="Q35" s="6"/>
-      <c r="R35" s="7"/>
-      <c r="S35" s="6"/>
-      <c r="T35" s="6"/>
-      <c r="U35" s="6"/>
-      <c r="V35" s="6"/>
-      <c r="W35" s="6"/>
-      <c r="X35" s="8"/>
-      <c r="Y35" s="6"/>
-      <c r="Z35" s="6"/>
-      <c r="AA35" s="8"/>
-      <c r="AB35" s="8"/>
-      <c r="AC35" s="8"/>
-      <c r="AD35" s="8"/>
-      <c r="AE35" s="6"/>
+      <c r="O35" s="5">
+        <v>3266.4200000000001</v>
+      </c>
+      <c r="P35" s="5">
+        <v>3266.4200000000001</v>
+      </c>
+      <c r="Q35" s="6">
+        <v>-0.16677210346410887</v>
+      </c>
+      <c r="R35" s="7">
+        <v>31</v>
+      </c>
+      <c r="S35" s="6">
+        <v>0.10714285714285721</v>
+      </c>
+      <c r="T35" s="6">
+        <v>3.3305821357939269</v>
+      </c>
+      <c r="U35" s="6">
+        <v>0.66339604215012149</v>
+      </c>
+      <c r="V35" s="6">
+        <v>0.25126208509622155</v>
+      </c>
+      <c r="W35" s="6">
+        <v>0.16931303996424218</v>
+      </c>
+      <c r="X35" s="8">
+        <v>36.914999999999999</v>
+      </c>
+      <c r="Y35" s="6">
+        <v>0.59999999999999998</v>
+      </c>
+      <c r="Z35" s="6">
+        <v>0.45000000000000001</v>
+      </c>
+      <c r="AA35" s="8">
+        <v>13.183334482758621</v>
+      </c>
+      <c r="AB35" s="8">
+        <v>4.3805555555555555</v>
+      </c>
+      <c r="AC35" s="8">
+        <v>18.126387999999999</v>
+      </c>
+      <c r="AD35" s="8">
+        <v>24.177500000000002</v>
+      </c>
+      <c r="AE35" s="6">
+        <v>0.29999999999999999</v>
+      </c>
       <c r="AF35" s="9"/>
-      <c r="AG35" s="5"/>
+      <c r="AG35" s="5">
+        <v>0</v>
+      </c>
       <c r="AH35" s="10">
         <v>5</v>
       </c>
@@ -5993,7 +6245,7 @@
         <v>19565</v>
       </c>
       <c r="B39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C39" s="4">
         <v>44</v>
@@ -6029,25 +6281,61 @@
       <c t="s" r="N39" s="4">
         <v>52</v>
       </c>
-      <c r="O39" s="5"/>
-      <c r="P39" s="5"/>
-      <c r="Q39" s="6"/>
-      <c r="R39" s="7"/>
-      <c r="S39" s="6"/>
-      <c r="T39" s="6"/>
-      <c r="U39" s="6"/>
-      <c r="V39" s="6"/>
-      <c r="W39" s="6"/>
-      <c r="X39" s="8"/>
-      <c r="Y39" s="6"/>
-      <c r="Z39" s="6"/>
-      <c r="AA39" s="8"/>
-      <c r="AB39" s="8"/>
-      <c r="AC39" s="8"/>
-      <c r="AD39" s="8"/>
-      <c r="AE39" s="6"/>
+      <c r="O39" s="5">
+        <v>5722.3299999999999</v>
+      </c>
+      <c r="P39" s="5">
+        <v>5722.3299999999999</v>
+      </c>
+      <c r="Q39" s="6">
+        <v>0.20928360101437016</v>
+      </c>
+      <c r="R39" s="7">
+        <v>65</v>
+      </c>
+      <c r="S39" s="6">
+        <v>0.14035087719298245</v>
+      </c>
+      <c r="T39" s="6">
+        <v>0.27796035880489239</v>
+      </c>
+      <c r="U39" s="6">
+        <v>-0.034576667196753771</v>
+      </c>
+      <c r="V39" s="6">
+        <v>0.086523147039754777</v>
+      </c>
+      <c r="W39" s="6">
+        <v>0.046120024535460206</v>
+      </c>
+      <c r="X39" s="8">
+        <v>19.914473684210527</v>
+      </c>
+      <c r="Y39" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z39" s="6">
+        <v>0.026315789473684209</v>
+      </c>
+      <c r="AA39" s="8">
+        <v>2.5966140625</v>
+      </c>
+      <c r="AB39" s="8">
+        <v>5.622668</v>
+      </c>
+      <c r="AC39" s="8">
+        <v>8.2524899999999999</v>
+      </c>
+      <c r="AD39" s="8">
+        <v>12.946052631578947</v>
+      </c>
+      <c r="AE39" s="6">
+        <v>0.89473684210526316</v>
+      </c>
       <c r="AF39" s="9"/>
-      <c r="AG39" s="5"/>
+      <c r="AG39" s="5">
+        <v>0</v>
+      </c>
       <c r="AH39" s="10">
         <v>4</v>
       </c>
@@ -6219,7 +6507,7 @@
         <v>19578</v>
       </c>
       <c r="B41" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C41" s="4">
         <v>44</v>
@@ -6255,27 +6543,61 @@
       <c t="s" r="N41" s="4">
         <v>52</v>
       </c>
-      <c r="O41" s="5"/>
-      <c r="P41" s="5"/>
-      <c r="Q41" s="6"/>
-      <c r="R41" s="7"/>
-      <c r="S41" s="6"/>
-      <c r="T41" s="6"/>
-      <c r="U41" s="6"/>
-      <c r="V41" s="6"/>
-      <c r="W41" s="6"/>
-      <c r="X41" s="8"/>
-      <c r="Y41" s="6"/>
-      <c r="Z41" s="6"/>
-      <c r="AA41" s="8"/>
-      <c r="AB41" s="8"/>
+      <c r="O41" s="5">
+        <v>4834.6599999999999</v>
+      </c>
+      <c r="P41" s="5">
+        <v>4834.6599999999999</v>
+      </c>
+      <c r="Q41" s="6">
+        <v>-0.1289873923994076</v>
+      </c>
+      <c r="R41" s="7">
+        <v>61</v>
+      </c>
+      <c r="S41" s="6">
+        <v>-0.061538461538461542</v>
+      </c>
+      <c r="T41" s="6">
+        <v>0.44333665655909621</v>
+      </c>
+      <c r="U41" s="6">
+        <v>0.098216213756499943</v>
+      </c>
+      <c r="V41" s="6">
+        <v>0.03887615675145719</v>
+      </c>
+      <c r="W41" s="6">
+        <v>-0.00041926422954251182</v>
+      </c>
+      <c r="X41" s="8">
+        <v>25.997334000000002</v>
+      </c>
+      <c r="Y41" s="6">
+        <v>0.38</v>
+      </c>
+      <c r="Z41" s="6">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="AA41" s="8">
+        <v>2.7788883333333336</v>
+      </c>
+      <c r="AB41" s="8">
+        <v>6.7906249999999995</v>
+      </c>
       <c r="AC41" s="8">
         <v>9.6449580000000008</v>
       </c>
-      <c r="AD41" s="8"/>
-      <c r="AE41" s="6"/>
+      <c r="AD41" s="8">
+        <v>15.131666000000001</v>
+      </c>
+      <c r="AE41" s="6">
+        <v>0.66000000000000003</v>
+      </c>
       <c r="AF41" s="9"/>
-      <c r="AG41" s="5"/>
+      <c r="AG41" s="5">
+        <v>0</v>
+      </c>
       <c r="AH41" s="10">
         <v>4</v>
       </c>
@@ -6411,7 +6733,7 @@
         <v>19580</v>
       </c>
       <c r="B43" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C43" s="4">
         <v>44</v>
@@ -6447,25 +6769,61 @@
       <c t="s" r="N43" s="4">
         <v>52</v>
       </c>
-      <c r="O43" s="5"/>
-      <c r="P43" s="5"/>
-      <c r="Q43" s="6"/>
-      <c r="R43" s="7"/>
-      <c r="S43" s="6"/>
-      <c r="T43" s="6"/>
-      <c r="U43" s="6"/>
-      <c r="V43" s="6"/>
-      <c r="W43" s="6"/>
-      <c r="X43" s="8"/>
-      <c r="Y43" s="6"/>
-      <c r="Z43" s="6"/>
-      <c r="AA43" s="8"/>
-      <c r="AB43" s="8"/>
-      <c r="AC43" s="8"/>
-      <c r="AD43" s="8"/>
-      <c r="AE43" s="6"/>
+      <c r="O43" s="5">
+        <v>5703.0699999999997</v>
+      </c>
+      <c r="P43" s="5">
+        <v>5703.0699999999997</v>
+      </c>
+      <c r="Q43" s="6">
+        <v>-0.23821844415740889</v>
+      </c>
+      <c r="R43" s="7">
+        <v>53</v>
+      </c>
+      <c r="S43" s="6">
+        <v>-0.30263157894736847</v>
+      </c>
+      <c r="T43" s="6">
+        <v>0.33831292619589098</v>
+      </c>
+      <c r="U43" s="6">
+        <v>-0.03115474647865097</v>
+      </c>
+      <c r="V43" s="6">
+        <v>0.073935967820840359</v>
+      </c>
+      <c r="W43" s="6">
+        <v>0.052095099656851482</v>
+      </c>
+      <c r="X43" s="8">
+        <v>34.325806451612898</v>
+      </c>
+      <c r="Y43" s="6">
+        <v>0.70588235294117652</v>
+      </c>
+      <c r="Z43" s="6">
+        <v>0.19354838709677419</v>
+      </c>
+      <c r="AA43" s="8">
+        <v>7.1644660377358491</v>
+      </c>
+      <c r="AB43" s="8">
+        <v>7.4868696969696966</v>
+      </c>
+      <c r="AC43" s="8">
+        <v>14.845691</v>
+      </c>
+      <c r="AD43" s="8">
+        <v>21.828281818181818</v>
+      </c>
+      <c r="AE43" s="6">
+        <v>0.22580645161290322</v>
+      </c>
       <c r="AF43" s="9"/>
-      <c r="AG43" s="5"/>
+      <c r="AG43" s="5">
+        <v>0</v>
+      </c>
       <c r="AH43" s="10">
         <v>1</v>
       </c>
@@ -7155,7 +7513,7 @@
         <v>19600</v>
       </c>
       <c r="B49" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C49" s="4">
         <v>44</v>
@@ -7189,25 +7547,61 @@
       <c t="s" r="N49" s="4">
         <v>52</v>
       </c>
-      <c r="O49" s="5"/>
-      <c r="P49" s="5"/>
-      <c r="Q49" s="6"/>
-      <c r="R49" s="7"/>
-      <c r="S49" s="6"/>
-      <c r="T49" s="6"/>
-      <c r="U49" s="6"/>
-      <c r="V49" s="6"/>
-      <c r="W49" s="6"/>
-      <c r="X49" s="8"/>
-      <c r="Y49" s="6"/>
-      <c r="Z49" s="6"/>
-      <c r="AA49" s="8"/>
-      <c r="AB49" s="8"/>
-      <c r="AC49" s="8"/>
-      <c r="AD49" s="8"/>
-      <c r="AE49" s="6"/>
+      <c r="O49" s="5">
+        <v>4099.6599999999999</v>
+      </c>
+      <c r="P49" s="5">
+        <v>4099.6599999999999</v>
+      </c>
+      <c r="Q49" s="6">
+        <v>-0.32761816040753</v>
+      </c>
+      <c r="R49" s="7">
+        <v>50</v>
+      </c>
+      <c r="S49" s="6">
+        <v>-0.34210526315789469</v>
+      </c>
+      <c r="T49" s="6">
+        <v>0.013188898591590522</v>
+      </c>
+      <c r="U49" s="6">
+        <v>-0.33350082689784033</v>
+      </c>
+      <c r="V49" s="6">
+        <v>0.060080714010430136</v>
+      </c>
+      <c r="W49" s="6">
+        <v>0.047038169018894252</v>
+      </c>
+      <c r="X49" s="8">
+        <v>25.833332352941177</v>
+      </c>
+      <c r="Y49" s="6">
+        <v>0.88235294117647056</v>
+      </c>
+      <c r="Z49" s="6">
+        <v>0.088235294117647065</v>
+      </c>
+      <c r="AA49" s="8">
+        <v>3.2907808510638294</v>
+      </c>
+      <c r="AB49" s="8">
+        <v>4.438726470588235</v>
+      </c>
+      <c r="AC49" s="8">
+        <v>7.5348030000000001</v>
+      </c>
+      <c r="AD49" s="8">
+        <v>15.472058823529411</v>
+      </c>
+      <c r="AE49" s="6">
+        <v>0.70588235294117652</v>
+      </c>
       <c r="AF49" s="9"/>
-      <c r="AG49" s="5"/>
+      <c r="AG49" s="5">
+        <v>-1405.9000000000001</v>
+      </c>
       <c r="AH49" s="10">
         <v>3</v>
       </c>
@@ -7645,7 +8039,9 @@
       <c r="AB53" s="8">
         <v>3.2041649999999997</v>
       </c>
-      <c r="AC53" s="8"/>
+      <c r="AC53" s="8">
+        <v>6.1691659999999997</v>
+      </c>
       <c r="AD53" s="8">
         <v>13.111664999999999</v>
       </c>
@@ -7827,7 +8223,7 @@
         <v>19615</v>
       </c>
       <c r="B55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C55" s="4">
         <v>44</v>
@@ -7863,25 +8259,61 @@
       <c t="s" r="N55" s="4">
         <v>52</v>
       </c>
-      <c r="O55" s="5"/>
-      <c r="P55" s="5"/>
-      <c r="Q55" s="6"/>
-      <c r="R55" s="7"/>
-      <c r="S55" s="6"/>
-      <c r="T55" s="6"/>
-      <c r="U55" s="6"/>
-      <c r="V55" s="6"/>
-      <c r="W55" s="6"/>
-      <c r="X55" s="8"/>
-      <c r="Y55" s="6"/>
-      <c r="Z55" s="6"/>
-      <c r="AA55" s="8"/>
-      <c r="AB55" s="8"/>
-      <c r="AC55" s="8"/>
-      <c r="AD55" s="8"/>
-      <c r="AE55" s="6"/>
+      <c r="O55" s="5">
+        <v>4916.8999999999996</v>
+      </c>
+      <c r="P55" s="5">
+        <v>4916.8999999999996</v>
+      </c>
+      <c r="Q55" s="6">
+        <v>-0.22049612142561592</v>
+      </c>
+      <c r="R55" s="7">
+        <v>59</v>
+      </c>
+      <c r="S55" s="6">
+        <v>-0.13235294117647056</v>
+      </c>
+      <c r="T55" s="6">
+        <v>0.00016880554821127133</v>
+      </c>
+      <c r="U55" s="6">
+        <v>-0.38203746262889221</v>
+      </c>
+      <c r="V55" s="6">
+        <v>0.11899825093046432</v>
+      </c>
+      <c r="W55" s="6">
+        <v>0.075308120970530218</v>
+      </c>
+      <c r="X55" s="8">
+        <v>28.163179069767441</v>
+      </c>
+      <c r="Y55" s="6">
+        <v>0.18181818181818182</v>
+      </c>
+      <c r="Z55" s="6">
+        <v>0.11627906976744186</v>
+      </c>
+      <c r="AA55" s="8">
+        <v>3.0197921874999998</v>
+      </c>
+      <c r="AB55" s="8">
+        <v>8.894960465116279</v>
+      </c>
+      <c r="AC55" s="8">
+        <v>11.822044</v>
+      </c>
+      <c r="AD55" s="8">
+        <v>18.494318181818183</v>
+      </c>
+      <c r="AE55" s="6">
+        <v>0.69767441860465118</v>
+      </c>
       <c r="AF55" s="9"/>
-      <c r="AG55" s="5"/>
+      <c r="AG55" s="5">
+        <v>0</v>
+      </c>
       <c r="AH55" s="10">
         <v>2</v>
       </c>
@@ -8182,7 +8614,7 @@
         <v>19618</v>
       </c>
       <c r="B58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C58" s="4">
         <v>44</v>
@@ -8218,25 +8650,59 @@
       <c t="s" r="N58" s="4">
         <v>52</v>
       </c>
-      <c r="O58" s="5"/>
-      <c r="P58" s="5"/>
-      <c r="Q58" s="6"/>
-      <c r="R58" s="7"/>
-      <c r="S58" s="6"/>
-      <c r="T58" s="6"/>
-      <c r="U58" s="6"/>
-      <c r="V58" s="6"/>
-      <c r="W58" s="6"/>
-      <c r="X58" s="8"/>
-      <c r="Y58" s="6"/>
-      <c r="Z58" s="6"/>
-      <c r="AA58" s="8"/>
-      <c r="AB58" s="8"/>
+      <c r="O58" s="5">
+        <v>6474.2200000000003</v>
+      </c>
+      <c r="P58" s="5">
+        <v>6474.2200000000003</v>
+      </c>
+      <c r="Q58" s="6">
+        <v>-0.0021700599540711574</v>
+      </c>
+      <c r="R58" s="7">
+        <v>75</v>
+      </c>
+      <c r="S58" s="6">
+        <v>0.086956521739130377</v>
+      </c>
+      <c r="T58" s="6">
+        <v>-0.053047733935516553</v>
+      </c>
+      <c r="U58" s="6">
+        <v>-0.46804444396390604</v>
+      </c>
+      <c r="V58" s="6">
+        <v>0.014939251369276915</v>
+      </c>
+      <c r="W58" s="6">
+        <v>0.00130517653091801</v>
+      </c>
+      <c r="X58" s="8">
+        <v>22.586217307692309</v>
+      </c>
+      <c r="Y58" s="6">
+        <v>0.57692307692307687</v>
+      </c>
+      <c r="Z58" s="6">
+        <v>0.019230769230769232</v>
+      </c>
+      <c r="AA58" s="8">
+        <v>2.8065732394366196</v>
+      </c>
+      <c r="AB58" s="8">
+        <v>4.1423076923076927</v>
+      </c>
       <c r="AC58" s="8"/>
-      <c r="AD58" s="8"/>
-      <c r="AE58" s="6"/>
+      <c r="AD58" s="8">
+        <v>14.096153846153847</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>0.86538461538461542</v>
+      </c>
       <c r="AF58" s="9"/>
-      <c r="AG58" s="5"/>
+      <c r="AG58" s="5">
+        <v>-185</v>
+      </c>
       <c r="AH58" s="10">
         <v>2</v>
       </c>
@@ -8408,7 +8874,7 @@
         <v>19623</v>
       </c>
       <c r="B60" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C60" s="4">
         <v>44</v>
@@ -8444,25 +8910,61 @@
       <c t="s" r="N60" s="4">
         <v>52</v>
       </c>
-      <c r="O60" s="5"/>
-      <c r="P60" s="5"/>
-      <c r="Q60" s="6"/>
-      <c r="R60" s="7"/>
-      <c r="S60" s="6"/>
-      <c r="T60" s="6"/>
-      <c r="U60" s="6"/>
-      <c r="V60" s="6"/>
-      <c r="W60" s="6"/>
-      <c r="X60" s="8"/>
-      <c r="Y60" s="6"/>
-      <c r="Z60" s="6"/>
-      <c r="AA60" s="8"/>
-      <c r="AB60" s="8"/>
-      <c r="AC60" s="8"/>
-      <c r="AD60" s="8"/>
-      <c r="AE60" s="6"/>
+      <c r="O60" s="5">
+        <v>2864.4000000000001</v>
+      </c>
+      <c r="P60" s="5">
+        <v>2864.4000000000001</v>
+      </c>
+      <c r="Q60" s="6">
+        <v>-0.14532005740833009</v>
+      </c>
+      <c r="R60" s="7">
+        <v>31</v>
+      </c>
+      <c r="S60" s="6">
+        <v>-0.31111111111111112</v>
+      </c>
+      <c r="T60" s="6">
+        <v>0.30907188241865663</v>
+      </c>
+      <c r="U60" s="6">
+        <v>-0.030224305264627844</v>
+      </c>
+      <c r="V60" s="6">
+        <v>0.074983766233766236</v>
+      </c>
+      <c r="W60" s="6">
+        <v>0.036029709537774054</v>
+      </c>
+      <c r="X60" s="8">
+        <v>21.520515384615386</v>
+      </c>
+      <c r="Y60" s="6">
+        <v>0.84615384615384615</v>
+      </c>
+      <c r="Z60" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA60" s="8">
+        <v>3.1919354838709677</v>
+      </c>
+      <c r="AB60" s="8">
+        <v>2.3294846153846156</v>
+      </c>
+      <c r="AC60" s="8">
+        <v>5.983333</v>
+      </c>
+      <c r="AD60" s="8">
+        <v>13.939746153846155</v>
+      </c>
+      <c r="AE60" s="6">
+        <v>1</v>
+      </c>
       <c r="AF60" s="9"/>
-      <c r="AG60" s="5"/>
+      <c r="AG60" s="5">
+        <v>0</v>
+      </c>
       <c r="AH60" s="10">
         <v>4</v>
       </c>
@@ -9765,7 +10267,7 @@
         <v>19649</v>
       </c>
       <c r="B71" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C71" s="4">
         <v>44</v>
@@ -9799,25 +10301,61 @@
       <c t="s" r="N71" s="4">
         <v>52</v>
       </c>
-      <c r="O71" s="5"/>
-      <c r="P71" s="5"/>
-      <c r="Q71" s="6"/>
-      <c r="R71" s="7"/>
-      <c r="S71" s="6"/>
-      <c r="T71" s="6"/>
-      <c r="U71" s="6"/>
-      <c r="V71" s="6"/>
-      <c r="W71" s="6"/>
-      <c r="X71" s="8"/>
-      <c r="Y71" s="6"/>
-      <c r="Z71" s="6"/>
-      <c r="AA71" s="8"/>
-      <c r="AB71" s="8"/>
-      <c r="AC71" s="8"/>
-      <c r="AD71" s="8"/>
-      <c r="AE71" s="6"/>
+      <c r="O71" s="5">
+        <v>5556.5900000000001</v>
+      </c>
+      <c r="P71" s="5">
+        <v>5556.5900000000001</v>
+      </c>
+      <c r="Q71" s="6">
+        <v>0.073421912790832433</v>
+      </c>
+      <c r="R71" s="7">
+        <v>62</v>
+      </c>
+      <c r="S71" s="6">
+        <v>-0.060606060606060552</v>
+      </c>
+      <c r="T71" s="6">
+        <v>0.30972571307222596</v>
+      </c>
+      <c r="U71" s="6">
+        <v>-0.02891003295186436</v>
+      </c>
+      <c r="V71" s="6">
+        <v>0.061827397738541089</v>
+      </c>
+      <c r="W71" s="6">
+        <v>0.01274153752571271</v>
+      </c>
+      <c r="X71" s="8">
+        <v>22.889332</v>
+      </c>
+      <c r="Y71" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z71" s="6">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="AA71" s="8">
+        <v>2.9592901639344258</v>
+      </c>
+      <c r="AB71" s="8">
+        <v>5.5393320000000008</v>
+      </c>
+      <c r="AC71" s="8">
+        <v>8.7073330000000002</v>
+      </c>
+      <c r="AD71" s="8">
+        <v>16.655332000000001</v>
+      </c>
+      <c r="AE71" s="6">
+        <v>0.92000000000000004</v>
+      </c>
       <c r="AF71" s="9"/>
-      <c r="AG71" s="5"/>
+      <c r="AG71" s="5">
+        <v>-347</v>
+      </c>
       <c r="AH71" s="10">
         <v>4</v>
       </c>
@@ -10207,7 +10745,7 @@
         <v>19657</v>
       </c>
       <c r="B75" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C75" s="4">
         <v>44</v>
@@ -10243,25 +10781,61 @@
       <c t="s" r="N75" s="4">
         <v>52</v>
       </c>
-      <c r="O75" s="5"/>
-      <c r="P75" s="5"/>
-      <c r="Q75" s="6"/>
-      <c r="R75" s="7"/>
-      <c r="S75" s="6"/>
-      <c r="T75" s="6"/>
-      <c r="U75" s="6"/>
-      <c r="V75" s="6"/>
-      <c r="W75" s="6"/>
-      <c r="X75" s="8"/>
-      <c r="Y75" s="6"/>
-      <c r="Z75" s="6"/>
-      <c r="AA75" s="8"/>
-      <c r="AB75" s="8"/>
-      <c r="AC75" s="8"/>
-      <c r="AD75" s="8"/>
-      <c r="AE75" s="6"/>
+      <c r="O75" s="5">
+        <v>4030.9099999999999</v>
+      </c>
+      <c r="P75" s="5">
+        <v>4030.9099999999999</v>
+      </c>
+      <c r="Q75" s="6">
+        <v>-0.16122836697026255</v>
+      </c>
+      <c r="R75" s="7">
+        <v>42</v>
+      </c>
+      <c r="S75" s="6">
+        <v>-0.125</v>
+      </c>
+      <c r="T75" s="6">
+        <v>0</v>
+      </c>
+      <c r="U75" s="6">
+        <v>-0.3607423633869275</v>
+      </c>
+      <c r="V75" s="6">
+        <v>0.076609624129538992</v>
+      </c>
+      <c r="W75" s="6">
+        <v>0.049935746518776157</v>
+      </c>
+      <c r="X75" s="8">
+        <v>21.71573888888889</v>
+      </c>
+      <c r="Y75" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="8">
+        <v>5.3158738095238096</v>
+      </c>
+      <c r="AB75" s="8">
+        <v>5.3379611111111105</v>
+      </c>
+      <c r="AC75" s="8">
+        <v>10.123049</v>
+      </c>
+      <c r="AD75" s="8">
+        <v>16.980555555555554</v>
+      </c>
+      <c r="AE75" s="6">
+        <v>0.94444444444444442</v>
+      </c>
       <c r="AF75" s="9"/>
-      <c r="AG75" s="5"/>
+      <c r="AG75" s="5">
+        <v>-504.60000000000002</v>
+      </c>
       <c r="AH75" s="10">
         <v>3</v>
       </c>
@@ -10653,7 +11227,7 @@
         <v>19671</v>
       </c>
       <c r="B79" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C79" s="4">
         <v>44</v>
@@ -10689,25 +11263,61 @@
       <c t="s" r="N79" s="4">
         <v>52</v>
       </c>
-      <c r="O79" s="5"/>
-      <c r="P79" s="5"/>
-      <c r="Q79" s="6"/>
-      <c r="R79" s="7"/>
-      <c r="S79" s="6"/>
-      <c r="T79" s="6"/>
-      <c r="U79" s="6"/>
-      <c r="V79" s="6"/>
-      <c r="W79" s="6"/>
-      <c r="X79" s="8"/>
-      <c r="Y79" s="6"/>
-      <c r="Z79" s="6"/>
-      <c r="AA79" s="8"/>
-      <c r="AB79" s="8"/>
-      <c r="AC79" s="8"/>
-      <c r="AD79" s="8"/>
-      <c r="AE79" s="6"/>
+      <c r="O79" s="5">
+        <v>6626.5500000000002</v>
+      </c>
+      <c r="P79" s="5">
+        <v>6626.5500000000002</v>
+      </c>
+      <c r="Q79" s="6">
+        <v>0.070352124051041853</v>
+      </c>
+      <c r="R79" s="7">
+        <v>65</v>
+      </c>
+      <c r="S79" s="6">
+        <v>-0.029850746268656692</v>
+      </c>
+      <c r="T79" s="6">
+        <v>0.44454281639767296</v>
+      </c>
+      <c r="U79" s="6">
+        <v>0.060708090937214687</v>
+      </c>
+      <c r="V79" s="6">
+        <v>0.036833420105484752</v>
+      </c>
+      <c r="W79" s="6">
+        <v>0.028059623786133057</v>
+      </c>
+      <c r="X79" s="8">
+        <v>30.444827586206895</v>
+      </c>
+      <c r="Y79" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z79" s="6">
+        <v>0.13793103448275862</v>
+      </c>
+      <c r="AA79" s="8">
+        <v>6.9835892307692307</v>
+      </c>
+      <c r="AB79" s="8">
+        <v>13.084482758620689</v>
+      </c>
+      <c r="AC79" s="8">
+        <v>19.528734</v>
+      </c>
+      <c r="AD79" s="8">
+        <v>26.472989655172412</v>
+      </c>
+      <c r="AE79" s="6">
+        <v>0.51724137931034486</v>
+      </c>
       <c r="AF79" s="9"/>
-      <c r="AG79" s="5"/>
+      <c r="AG79" s="5">
+        <v>-310.89999999999998</v>
+      </c>
       <c r="AH79" s="10">
         <v>3</v>
       </c>
@@ -11980,7 +12590,7 @@
         <v>19694</v>
       </c>
       <c r="B90" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C90" s="4">
         <v>44</v>
@@ -12016,25 +12626,61 @@
       <c t="s" r="N90" s="4">
         <v>52</v>
       </c>
-      <c r="O90" s="5"/>
-      <c r="P90" s="5"/>
-      <c r="Q90" s="6"/>
-      <c r="R90" s="7"/>
-      <c r="S90" s="6"/>
-      <c r="T90" s="6"/>
-      <c r="U90" s="6"/>
-      <c r="V90" s="6"/>
-      <c r="W90" s="6"/>
-      <c r="X90" s="8"/>
-      <c r="Y90" s="6"/>
-      <c r="Z90" s="6"/>
-      <c r="AA90" s="8"/>
-      <c r="AB90" s="8"/>
-      <c r="AC90" s="8"/>
-      <c r="AD90" s="8"/>
-      <c r="AE90" s="6"/>
+      <c r="O90" s="5">
+        <v>4447.1300000000001</v>
+      </c>
+      <c r="P90" s="5">
+        <v>4447.1300000000001</v>
+      </c>
+      <c r="Q90" s="6">
+        <v>0.064688658895408757</v>
+      </c>
+      <c r="R90" s="7">
+        <v>52</v>
+      </c>
+      <c r="S90" s="6">
+        <v>0.1063829787234043</v>
+      </c>
+      <c r="T90" s="6">
+        <v>0</v>
+      </c>
+      <c r="U90" s="6">
+        <v>-3.1814765927688193</v>
+      </c>
+      <c r="V90" s="6">
+        <v>0.15717800019338313</v>
+      </c>
+      <c r="W90" s="6">
+        <v>0.11117979460910744</v>
+      </c>
+      <c r="X90" s="8">
+        <v>32.439783870967737</v>
+      </c>
+      <c r="Y90" s="6">
+        <v>0.54838709677419351</v>
+      </c>
+      <c r="Z90" s="6">
+        <v>0.22580645161290322</v>
+      </c>
+      <c r="AA90" s="8">
+        <v>4.9066660000000004</v>
+      </c>
+      <c r="AB90" s="8">
+        <v>18.616667741935483</v>
+      </c>
+      <c r="AC90" s="8">
+        <v>21.746773000000001</v>
+      </c>
+      <c r="AD90" s="8">
+        <v>28.677419354838708</v>
+      </c>
+      <c r="AE90" s="6">
+        <v>0.64516129032258063</v>
+      </c>
       <c r="AF90" s="9"/>
-      <c r="AG90" s="5"/>
+      <c r="AG90" s="5">
+        <v>0</v>
+      </c>
       <c r="AH90" s="10">
         <v>2</v>
       </c>
@@ -14313,7 +14959,7 @@
         <v>19730</v>
       </c>
       <c r="B109" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C109" s="4">
         <v>44</v>
@@ -14347,25 +14993,61 @@
       <c t="s" r="N109" s="4">
         <v>52</v>
       </c>
-      <c r="O109" s="5"/>
-      <c r="P109" s="5"/>
-      <c r="Q109" s="6"/>
-      <c r="R109" s="7"/>
-      <c r="S109" s="6"/>
-      <c r="T109" s="6"/>
-      <c r="U109" s="6"/>
-      <c r="V109" s="6"/>
-      <c r="W109" s="6"/>
-      <c r="X109" s="8"/>
-      <c r="Y109" s="6"/>
-      <c r="Z109" s="6"/>
-      <c r="AA109" s="8"/>
-      <c r="AB109" s="8"/>
-      <c r="AC109" s="8"/>
-      <c r="AD109" s="8"/>
-      <c r="AE109" s="6"/>
+      <c r="O109" s="5">
+        <v>6606.1000000000004</v>
+      </c>
+      <c r="P109" s="5">
+        <v>6606.1000000000004</v>
+      </c>
+      <c r="Q109" s="6">
+        <v>-0.13995391285102399</v>
+      </c>
+      <c r="R109" s="7">
+        <v>65</v>
+      </c>
+      <c r="S109" s="6">
+        <v>-0.16666666666666663</v>
+      </c>
+      <c r="T109" s="6">
+        <v>5.4398339262197064</v>
+      </c>
+      <c r="U109" s="6">
+        <v>5.0687677903755617</v>
+      </c>
+      <c r="V109" s="6">
+        <v>0.010671046457062412</v>
+      </c>
+      <c r="W109" s="6">
+        <v>-0.0049629887528193639</v>
+      </c>
+      <c r="X109" s="8">
+        <v>24.743333333333332</v>
+      </c>
+      <c r="Y109" s="6">
+        <v>0.73333333333333328</v>
+      </c>
+      <c r="Z109" s="6">
+        <v>0.066666666666666666</v>
+      </c>
+      <c r="AA109" s="8">
+        <v>4.9974742424242429</v>
+      </c>
+      <c r="AB109" s="8">
+        <v>7.808886666666667</v>
+      </c>
+      <c r="AC109" s="8">
+        <v>12.848471</v>
+      </c>
+      <c r="AD109" s="8">
+        <v>20.692220000000002</v>
+      </c>
+      <c r="AE109" s="6">
+        <v>0.73333333333333328</v>
+      </c>
       <c r="AF109" s="9"/>
-      <c r="AG109" s="5"/>
+      <c r="AG109" s="5">
+        <v>0</v>
+      </c>
       <c r="AH109" s="10">
         <v>2</v>
       </c>
@@ -15521,10 +16203,10 @@
         <v>-0.16363636363636369</v>
       </c>
       <c r="T119" s="6">
-        <v>0.32328164989850855</v>
+        <v>0.32060464654487686</v>
       </c>
       <c r="U119" s="6">
-        <v>-0.0058651597387697468</v>
+        <v>-0.0085421630924013767</v>
       </c>
       <c r="V119" s="6">
         <v>0.060880548936545757</v>
@@ -16079,7 +16761,7 @@
         <v>0</v>
       </c>
       <c r="AH123" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI123" s="11"/>
       <c r="AJ123" s="13">
@@ -17766,7 +18448,9 @@
       <c r="AB136" s="8">
         <v>6.7150809523809514</v>
       </c>
-      <c r="AC136" s="8"/>
+      <c r="AC136" s="8">
+        <v>13.870673999999999</v>
+      </c>
       <c r="AD136" s="8">
         <v>20.442061904761903</v>
       </c>
@@ -17946,7 +18630,7 @@
         <v>19788</v>
       </c>
       <c r="B138" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C138" s="4">
         <v>44</v>
@@ -17980,25 +18664,61 @@
       <c t="s" r="N138" s="4">
         <v>52</v>
       </c>
-      <c r="O138" s="5"/>
-      <c r="P138" s="5"/>
-      <c r="Q138" s="6"/>
-      <c r="R138" s="7"/>
-      <c r="S138" s="6"/>
-      <c r="T138" s="6"/>
-      <c r="U138" s="6"/>
-      <c r="V138" s="6"/>
-      <c r="W138" s="6"/>
-      <c r="X138" s="8"/>
-      <c r="Y138" s="6"/>
-      <c r="Z138" s="6"/>
-      <c r="AA138" s="8"/>
-      <c r="AB138" s="8"/>
-      <c r="AC138" s="8"/>
-      <c r="AD138" s="8"/>
-      <c r="AE138" s="6"/>
+      <c r="O138" s="5">
+        <v>14484.02</v>
+      </c>
+      <c r="P138" s="5">
+        <v>14484.02</v>
+      </c>
+      <c r="Q138" s="6">
+        <v>0.072216065600226198</v>
+      </c>
+      <c r="R138" s="7">
+        <v>132</v>
+      </c>
+      <c r="S138" s="6">
+        <v>-0.036496350364963459</v>
+      </c>
+      <c r="T138" s="6">
+        <v>0.37489189465355616</v>
+      </c>
+      <c r="U138" s="6">
+        <v>0.025151283966744039</v>
+      </c>
+      <c r="V138" s="6">
+        <v>0.028013804178674152</v>
+      </c>
+      <c r="W138" s="6">
+        <v>0.0034253266703580909</v>
+      </c>
+      <c r="X138" s="8">
+        <v>24.886140000000001</v>
+      </c>
+      <c r="Y138" s="6">
+        <v>0.83157894736842108</v>
+      </c>
+      <c r="Z138" s="6">
+        <v>0.010526315789473684</v>
+      </c>
+      <c r="AA138" s="8">
+        <v>4.9892857142857139</v>
+      </c>
+      <c r="AB138" s="8">
+        <v>6.9005434782608699</v>
+      </c>
+      <c r="AC138" s="8">
+        <v>12.050542999999999</v>
+      </c>
+      <c r="AD138" s="8">
+        <v>18.395965263157894</v>
+      </c>
+      <c r="AE138" s="6">
+        <v>0.83157894736842108</v>
+      </c>
       <c r="AF138" s="9"/>
-      <c r="AG138" s="5"/>
+      <c r="AG138" s="5">
+        <v>-677.28999999999996</v>
+      </c>
       <c r="AH138" s="10">
         <v>3</v>
       </c>
@@ -20882,7 +21602,7 @@
         <v>19872</v>
       </c>
       <c r="B162" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C162" s="4">
         <v>44</v>
@@ -20918,25 +21638,61 @@
       <c t="s" r="N162" s="4">
         <v>52</v>
       </c>
-      <c r="O162" s="5"/>
-      <c r="P162" s="5"/>
-      <c r="Q162" s="6"/>
-      <c r="R162" s="7"/>
-      <c r="S162" s="6"/>
-      <c r="T162" s="6"/>
-      <c r="U162" s="6"/>
-      <c r="V162" s="6"/>
-      <c r="W162" s="6"/>
-      <c r="X162" s="8"/>
-      <c r="Y162" s="6"/>
-      <c r="Z162" s="6"/>
-      <c r="AA162" s="8"/>
-      <c r="AB162" s="8"/>
-      <c r="AC162" s="8"/>
-      <c r="AD162" s="8"/>
-      <c r="AE162" s="6"/>
+      <c r="O162" s="5">
+        <v>4879.4300000000003</v>
+      </c>
+      <c r="P162" s="5">
+        <v>4879.4300000000003</v>
+      </c>
+      <c r="Q162" s="6">
+        <v>-0.026192106045698438</v>
+      </c>
+      <c r="R162" s="7">
+        <v>50</v>
+      </c>
+      <c r="S162" s="6">
+        <v>-0.20634920634920639</v>
+      </c>
+      <c r="T162" s="6">
+        <v>0.37908208540751687</v>
+      </c>
+      <c r="U162" s="6">
+        <v>0.010223427736436428</v>
+      </c>
+      <c r="V162" s="6">
+        <v>0.042388557679892934</v>
+      </c>
+      <c r="W162" s="6">
+        <v>0.025652996354082341</v>
+      </c>
+      <c r="X162" s="8">
+        <v>24.909720833333335</v>
+      </c>
+      <c r="Y162" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="Z162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA162" s="8">
+        <v>7.4937499999999995</v>
+      </c>
+      <c r="AB162" s="8">
+        <v>3.4493041666666664</v>
+      </c>
+      <c r="AC162" s="8">
+        <v>11.616666</v>
+      </c>
+      <c r="AD162" s="8">
+        <v>19.559029166666665</v>
+      </c>
+      <c r="AE162" s="6">
+        <v>0.875</v>
+      </c>
       <c r="AF162" s="9"/>
-      <c r="AG162" s="5"/>
+      <c r="AG162" s="5">
+        <v>-99.400000000000006</v>
+      </c>
       <c r="AH162" s="10">
         <v>2</v>
       </c>
@@ -22120,7 +22876,7 @@
         <v>19890</v>
       </c>
       <c r="B172" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C172" s="4">
         <v>44</v>
@@ -22156,25 +22912,61 @@
       <c t="s" r="N172" s="4">
         <v>52</v>
       </c>
-      <c r="O172" s="5"/>
-      <c r="P172" s="5"/>
-      <c r="Q172" s="6"/>
-      <c r="R172" s="7"/>
-      <c r="S172" s="6"/>
-      <c r="T172" s="6"/>
-      <c r="U172" s="6"/>
-      <c r="V172" s="6"/>
-      <c r="W172" s="6"/>
-      <c r="X172" s="8"/>
-      <c r="Y172" s="6"/>
-      <c r="Z172" s="6"/>
-      <c r="AA172" s="8"/>
-      <c r="AB172" s="8"/>
-      <c r="AC172" s="8"/>
-      <c r="AD172" s="8"/>
-      <c r="AE172" s="6"/>
+      <c r="O172" s="5">
+        <v>2115.2399999999998</v>
+      </c>
+      <c r="P172" s="5">
+        <v>2115.2399999999998</v>
+      </c>
+      <c r="Q172" s="6">
+        <v>0.063469079939667994</v>
+      </c>
+      <c r="R172" s="7">
+        <v>24</v>
+      </c>
+      <c r="S172" s="6">
+        <v>-0.040000000000000036</v>
+      </c>
+      <c r="T172" s="6">
+        <v>0.30320247347818691</v>
+      </c>
+      <c r="U172" s="6">
+        <v>0.0084935988351203667</v>
+      </c>
+      <c r="V172" s="6">
+        <v>0.050165938616894543</v>
+      </c>
+      <c r="W172" s="6">
+        <v>-0.011912123446984739</v>
+      </c>
+      <c r="X172" s="8">
+        <v>24.370835</v>
+      </c>
+      <c r="Y172" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z172" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA172" s="8">
+        <v>5.568117391304348</v>
+      </c>
+      <c r="AB172" s="8">
+        <v>6.2625000000000002</v>
+      </c>
+      <c r="AC172" s="8">
+        <v>12.18</v>
+      </c>
+      <c r="AD172" s="8">
+        <v>19.141665</v>
+      </c>
+      <c r="AE172" s="6">
+        <v>0.90000000000000002</v>
+      </c>
       <c r="AF172" s="9"/>
-      <c r="AG172" s="5"/>
+      <c r="AG172" s="5">
+        <v>0</v>
+      </c>
       <c r="AH172" s="10">
         <v>1</v>
       </c>
@@ -22608,7 +23400,7 @@
         <v>19898</v>
       </c>
       <c r="B176" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C176" s="4">
         <v>44</v>
@@ -22642,25 +23434,61 @@
       <c t="s" r="N176" s="4">
         <v>52</v>
       </c>
-      <c r="O176" s="5"/>
-      <c r="P176" s="5"/>
-      <c r="Q176" s="6"/>
-      <c r="R176" s="7"/>
-      <c r="S176" s="6"/>
-      <c r="T176" s="6"/>
-      <c r="U176" s="6"/>
-      <c r="V176" s="6"/>
-      <c r="W176" s="6"/>
-      <c r="X176" s="8"/>
-      <c r="Y176" s="6"/>
-      <c r="Z176" s="6"/>
-      <c r="AA176" s="8"/>
-      <c r="AB176" s="8"/>
-      <c r="AC176" s="8"/>
-      <c r="AD176" s="8"/>
-      <c r="AE176" s="6"/>
+      <c r="O176" s="5">
+        <v>3484.2399999999998</v>
+      </c>
+      <c r="P176" s="5">
+        <v>3484.2399999999998</v>
+      </c>
+      <c r="Q176" s="6">
+        <v>0.39042571870959497</v>
+      </c>
+      <c r="R176" s="7">
+        <v>38</v>
+      </c>
+      <c r="S176" s="6">
+        <v>0.1875</v>
+      </c>
+      <c r="T176" s="6">
+        <v>0.008208389777971668</v>
+      </c>
+      <c r="U176" s="6">
+        <v>-0.35447902555507083</v>
+      </c>
+      <c r="V176" s="6">
+        <v>0.061217223842215236</v>
+      </c>
+      <c r="W176" s="6">
+        <v>0.023582043716850732</v>
+      </c>
+      <c r="X176" s="8">
+        <v>33.100667999999999</v>
+      </c>
+      <c r="Y176" s="6">
+        <v>0.44</v>
+      </c>
+      <c r="Z176" s="6">
+        <v>0.12</v>
+      </c>
+      <c r="AA176" s="8">
+        <v>3.6598282051282056</v>
+      </c>
+      <c r="AB176" s="8">
+        <v>13.888</v>
+      </c>
+      <c r="AC176" s="8">
+        <v>17.310434999999998</v>
+      </c>
+      <c r="AD176" s="8">
+        <v>24.254668000000002</v>
+      </c>
+      <c r="AE176" s="6">
+        <v>0.35999999999999999</v>
+      </c>
       <c r="AF176" s="9"/>
-      <c r="AG176" s="5"/>
+      <c r="AG176" s="5">
+        <v>0</v>
+      </c>
       <c r="AH176" s="10">
         <v>3</v>
       </c>
@@ -23088,7 +23916,7 @@
         <v>19908</v>
       </c>
       <c r="B180" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C180" s="4">
         <v>44</v>
@@ -23124,25 +23952,61 @@
       <c t="s" r="N180" s="4">
         <v>52</v>
       </c>
-      <c r="O180" s="5"/>
-      <c r="P180" s="5"/>
-      <c r="Q180" s="6"/>
-      <c r="R180" s="7"/>
-      <c r="S180" s="6"/>
-      <c r="T180" s="6"/>
-      <c r="U180" s="6"/>
-      <c r="V180" s="6"/>
-      <c r="W180" s="6"/>
-      <c r="X180" s="8"/>
-      <c r="Y180" s="6"/>
-      <c r="Z180" s="6"/>
-      <c r="AA180" s="8"/>
-      <c r="AB180" s="8"/>
-      <c r="AC180" s="8"/>
-      <c r="AD180" s="8"/>
-      <c r="AE180" s="6"/>
+      <c r="O180" s="5">
+        <v>2010.9000000000001</v>
+      </c>
+      <c r="P180" s="5">
+        <v>2010.9000000000001</v>
+      </c>
+      <c r="Q180" s="6">
+        <v>-0.60665453905287248</v>
+      </c>
+      <c r="R180" s="7">
+        <v>24</v>
+      </c>
+      <c r="S180" s="6">
+        <v>-0.61904761904761907</v>
+      </c>
+      <c r="T180" s="6">
+        <v>0</v>
+      </c>
+      <c r="U180" s="6">
+        <v>-0.35551743000646474</v>
+      </c>
+      <c r="V180" s="6">
+        <v>0.039697150529613603</v>
+      </c>
+      <c r="W180" s="6">
+        <v>-0.056702471530160621</v>
+      </c>
+      <c r="X180" s="8">
+        <v>47.114285714285714</v>
+      </c>
+      <c r="Y180" s="6">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="Z180" s="6">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AA180" s="8">
+        <v>5.1536217391304344</v>
+      </c>
+      <c r="AB180" s="8">
+        <v>32.661899999999996</v>
+      </c>
+      <c r="AC180" s="8">
+        <v>37.576188999999999</v>
+      </c>
+      <c r="AD180" s="8">
+        <v>45.523814285714288</v>
+      </c>
+      <c r="AE180" s="6">
+        <v>0.14285714285714285</v>
+      </c>
       <c r="AF180" s="9"/>
-      <c r="AG180" s="5"/>
+      <c r="AG180" s="5">
+        <v>-30.5</v>
+      </c>
       <c r="AH180" s="10">
         <v>2</v>
       </c>
@@ -23183,7 +24047,7 @@
         <v>19910</v>
       </c>
       <c r="B181" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C181" s="4">
         <v>44</v>
@@ -23219,25 +24083,61 @@
       <c t="s" r="N181" s="4">
         <v>52</v>
       </c>
-      <c r="O181" s="5"/>
-      <c r="P181" s="5"/>
-      <c r="Q181" s="6"/>
-      <c r="R181" s="7"/>
-      <c r="S181" s="6"/>
-      <c r="T181" s="6"/>
-      <c r="U181" s="6"/>
-      <c r="V181" s="6"/>
-      <c r="W181" s="6"/>
-      <c r="X181" s="8"/>
-      <c r="Y181" s="6"/>
-      <c r="Z181" s="6"/>
-      <c r="AA181" s="8"/>
-      <c r="AB181" s="8"/>
-      <c r="AC181" s="8"/>
-      <c r="AD181" s="8"/>
-      <c r="AE181" s="6"/>
+      <c r="O181" s="5">
+        <v>2879.1999999999998</v>
+      </c>
+      <c r="P181" s="5">
+        <v>2879.1999999999998</v>
+      </c>
+      <c r="Q181" s="6">
+        <v>0.023242590091690829</v>
+      </c>
+      <c r="R181" s="7">
+        <v>31</v>
+      </c>
+      <c r="S181" s="6">
+        <v>0.033333333333333437</v>
+      </c>
+      <c r="T181" s="6">
+        <v>0.011965129202556267</v>
+      </c>
+      <c r="U181" s="6">
+        <v>-0.31715754376215616</v>
+      </c>
+      <c r="V181" s="6">
+        <v>0.06314774937482634</v>
+      </c>
+      <c r="W181" s="6">
+        <v>0.027821964434565159</v>
+      </c>
+      <c r="X181" s="8">
+        <v>13.960418750000001</v>
+      </c>
+      <c r="Y181" s="6">
+        <v>0.88235294117647056</v>
+      </c>
+      <c r="Z181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA181" s="8">
+        <v>3.0472233333333336</v>
+      </c>
+      <c r="AB181" s="8">
+        <v>3.3963000000000001</v>
+      </c>
+      <c r="AC181" s="8">
+        <v>6.1766880000000004</v>
+      </c>
+      <c r="AD181" s="8">
+        <v>10.31458125</v>
+      </c>
+      <c r="AE181" s="6">
+        <v>1</v>
+      </c>
       <c r="AF181" s="9"/>
-      <c r="AG181" s="5"/>
+      <c r="AG181" s="5">
+        <v>0</v>
+      </c>
       <c r="AH181" s="10">
         <v>3</v>
       </c>
@@ -23895,7 +24795,7 @@
         <v>19927</v>
       </c>
       <c r="B187" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C187" s="4">
         <v>44</v>
@@ -23931,25 +24831,61 @@
       <c t="s" r="N187" s="4">
         <v>52</v>
       </c>
-      <c r="O187" s="5"/>
-      <c r="P187" s="5"/>
-      <c r="Q187" s="6"/>
-      <c r="R187" s="7"/>
-      <c r="S187" s="6"/>
-      <c r="T187" s="6"/>
-      <c r="U187" s="6"/>
-      <c r="V187" s="6"/>
-      <c r="W187" s="6"/>
-      <c r="X187" s="8"/>
-      <c r="Y187" s="6"/>
-      <c r="Z187" s="6"/>
-      <c r="AA187" s="8"/>
-      <c r="AB187" s="8"/>
-      <c r="AC187" s="8"/>
-      <c r="AD187" s="8"/>
-      <c r="AE187" s="6"/>
+      <c r="O187" s="5">
+        <v>1151.45</v>
+      </c>
+      <c r="P187" s="5">
+        <v>1151.45</v>
+      </c>
+      <c r="Q187" s="6">
+        <v>-0.44296357215422566</v>
+      </c>
+      <c r="R187" s="7">
+        <v>17</v>
+      </c>
+      <c r="S187" s="6">
+        <v>-0.37037037037037035</v>
+      </c>
+      <c r="T187" s="6">
+        <v>0</v>
+      </c>
+      <c r="U187" s="6">
+        <v>-0.32851621868079373</v>
+      </c>
+      <c r="V187" s="6">
+        <v>0.18887533110425986</v>
+      </c>
+      <c r="W187" s="6">
+        <v>0.08811541968821919</v>
+      </c>
+      <c r="X187" s="8">
+        <v>39.136108333333333</v>
+      </c>
+      <c r="Y187" s="6">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="Z187" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="AA187" s="8">
+        <v>9.1029411764705888</v>
+      </c>
+      <c r="AB187" s="8">
+        <v>11.879166666666668</v>
+      </c>
+      <c r="AC187" s="8">
+        <v>20.926387999999999</v>
+      </c>
+      <c r="AD187" s="8">
+        <v>27.875</v>
+      </c>
+      <c r="AE187" s="6">
+        <v>0.33333333333333331</v>
+      </c>
       <c r="AF187" s="9"/>
-      <c r="AG187" s="5"/>
+      <c r="AG187" s="5">
+        <v>0</v>
+      </c>
       <c r="AH187" s="10">
         <v>1</v>
       </c>
@@ -24123,7 +25059,7 @@
         <v>19930</v>
       </c>
       <c r="B189" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C189" s="4">
         <v>44</v>
@@ -24159,25 +25095,61 @@
       <c t="s" r="N189" s="4">
         <v>52</v>
       </c>
-      <c r="O189" s="5"/>
-      <c r="P189" s="5"/>
-      <c r="Q189" s="6"/>
-      <c r="R189" s="7"/>
-      <c r="S189" s="6"/>
-      <c r="T189" s="6"/>
-      <c r="U189" s="6"/>
-      <c r="V189" s="6"/>
-      <c r="W189" s="6"/>
-      <c r="X189" s="8"/>
-      <c r="Y189" s="6"/>
-      <c r="Z189" s="6"/>
-      <c r="AA189" s="8"/>
-      <c r="AB189" s="8"/>
-      <c r="AC189" s="8"/>
-      <c r="AD189" s="8"/>
-      <c r="AE189" s="6"/>
+      <c r="O189" s="5">
+        <v>3247.3099999999999</v>
+      </c>
+      <c r="P189" s="5">
+        <v>3247.3099999999999</v>
+      </c>
+      <c r="Q189" s="6">
+        <v>0.11034329480954663</v>
+      </c>
+      <c r="R189" s="7">
+        <v>48</v>
+      </c>
+      <c r="S189" s="6">
+        <v>-0.11111111111111116</v>
+      </c>
+      <c r="T189" s="6">
+        <v>0.27351712648315069</v>
+      </c>
+      <c r="U189" s="6">
+        <v>-0.057252033221343201</v>
+      </c>
+      <c r="V189" s="6">
+        <v>0.070051211618231704</v>
+      </c>
+      <c r="W189" s="6">
+        <v>0.028952579211716775</v>
+      </c>
+      <c r="X189" s="8">
+        <v>29.410163414634148</v>
+      </c>
+      <c r="Y189" s="6">
+        <v>0.1951219512195122</v>
+      </c>
+      <c r="Z189" s="6">
+        <v>0.12195121951219512</v>
+      </c>
+      <c r="AA189" s="8">
+        <v>4.5746520833333335</v>
+      </c>
+      <c r="AB189" s="8">
+        <v>11.722763414634146</v>
+      </c>
+      <c r="AC189" s="8">
+        <v>16.438210999999999</v>
+      </c>
+      <c r="AD189" s="8">
+        <v>23.376829268292685</v>
+      </c>
+      <c r="AE189" s="6">
+        <v>0.6097560975609756</v>
+      </c>
       <c r="AF189" s="9"/>
-      <c r="AG189" s="5"/>
+      <c r="AG189" s="5">
+        <v>0</v>
+      </c>
       <c r="AH189" s="10">
         <v>3</v>
       </c>
@@ -24218,7 +25190,7 @@
         <v>19931</v>
       </c>
       <c r="B190" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C190" s="4">
         <v>44</v>
@@ -24254,25 +25226,61 @@
       <c t="s" r="N190" s="4">
         <v>52</v>
       </c>
-      <c r="O190" s="5"/>
-      <c r="P190" s="5"/>
-      <c r="Q190" s="6"/>
-      <c r="R190" s="7"/>
-      <c r="S190" s="6"/>
-      <c r="T190" s="6"/>
-      <c r="U190" s="6"/>
-      <c r="V190" s="6"/>
-      <c r="W190" s="6"/>
-      <c r="X190" s="8"/>
-      <c r="Y190" s="6"/>
-      <c r="Z190" s="6"/>
-      <c r="AA190" s="8"/>
-      <c r="AB190" s="8"/>
-      <c r="AC190" s="8"/>
-      <c r="AD190" s="8"/>
-      <c r="AE190" s="6"/>
+      <c r="O190" s="5">
+        <v>3058.8200000000002</v>
+      </c>
+      <c r="P190" s="5">
+        <v>3058.8200000000002</v>
+      </c>
+      <c r="Q190" s="6">
+        <v>-0.17697991163919513</v>
+      </c>
+      <c r="R190" s="7">
+        <v>34</v>
+      </c>
+      <c r="S190" s="6">
+        <v>-0.29166666666666663</v>
+      </c>
+      <c r="T190" s="6">
+        <v>0.04549332749230095</v>
+      </c>
+      <c r="U190" s="6">
+        <v>-0.47414169516349441</v>
+      </c>
+      <c r="V190" s="6">
+        <v>0.068469540541777549</v>
+      </c>
+      <c r="W190" s="6">
+        <v>0.03521815602094925</v>
+      </c>
+      <c r="X190" s="8">
+        <v>25.166662500000001</v>
+      </c>
+      <c r="Y190" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="Z190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA190" s="8">
+        <v>3.5284323529411767</v>
+      </c>
+      <c r="AB190" s="8">
+        <v>5.5250000000000004</v>
+      </c>
+      <c r="AC190" s="8">
+        <v>9.4020829999999993</v>
+      </c>
+      <c r="AD190" s="8">
+        <v>16.358337500000001</v>
+      </c>
+      <c r="AE190" s="6">
+        <v>0.625</v>
+      </c>
       <c r="AF190" s="9"/>
-      <c r="AG190" s="5"/>
+      <c r="AG190" s="5">
+        <v>0</v>
+      </c>
       <c r="AH190" s="10">
         <v>2</v>
       </c>
@@ -24835,7 +25843,7 @@
         <v>19944</v>
       </c>
       <c r="B195" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C195" s="4">
         <v>44</v>
@@ -24871,25 +25879,59 @@
       <c t="s" r="N195" s="4">
         <v>52</v>
       </c>
-      <c r="O195" s="5"/>
-      <c r="P195" s="5"/>
-      <c r="Q195" s="6"/>
-      <c r="R195" s="7"/>
-      <c r="S195" s="6"/>
-      <c r="T195" s="6"/>
-      <c r="U195" s="6"/>
-      <c r="V195" s="6"/>
-      <c r="W195" s="6"/>
-      <c r="X195" s="8"/>
-      <c r="Y195" s="6"/>
-      <c r="Z195" s="6"/>
-      <c r="AA195" s="8"/>
-      <c r="AB195" s="8"/>
+      <c r="O195" s="5">
+        <v>3466.1500000000001</v>
+      </c>
+      <c r="P195" s="5">
+        <v>3466.1500000000001</v>
+      </c>
+      <c r="Q195" s="6">
+        <v>0.063278596999266856</v>
+      </c>
+      <c r="R195" s="7">
+        <v>45</v>
+      </c>
+      <c r="S195" s="6">
+        <v>0.046511627906976827</v>
+      </c>
+      <c r="T195" s="6">
+        <v>0.34923001024191103</v>
+      </c>
+      <c r="U195" s="6">
+        <v>-0.0012914617082353619</v>
+      </c>
+      <c r="V195" s="6">
+        <v>0.018191365059215557</v>
+      </c>
+      <c r="W195" s="6">
+        <v>-0.014504854088830548</v>
+      </c>
+      <c r="X195" s="8">
+        <v>24.858973076923078</v>
+      </c>
+      <c r="Y195" s="6">
+        <v>0.69230769230769229</v>
+      </c>
+      <c r="Z195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA195" s="8">
+        <v>4.1811974358974355</v>
+      </c>
+      <c r="AB195" s="8">
+        <v>6.0012807692307693</v>
+      </c>
       <c r="AC195" s="8"/>
-      <c r="AD195" s="8"/>
-      <c r="AE195" s="6"/>
+      <c r="AD195" s="8">
+        <v>17.139742307692309</v>
+      </c>
+      <c r="AE195" s="6">
+        <v>0.88461538461538458</v>
+      </c>
       <c r="AF195" s="9"/>
-      <c r="AG195" s="5"/>
+      <c r="AG195" s="5">
+        <v>-173.5</v>
+      </c>
       <c r="AH195" s="10">
         <v>2</v>
       </c>
@@ -25323,7 +26365,7 @@
         <v>19951</v>
       </c>
       <c r="B199" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C199" s="4">
         <v>44</v>
@@ -25359,25 +26401,61 @@
       <c t="s" r="N199" s="4">
         <v>52</v>
       </c>
-      <c r="O199" s="5"/>
-      <c r="P199" s="5"/>
-      <c r="Q199" s="6"/>
-      <c r="R199" s="7"/>
-      <c r="S199" s="6"/>
-      <c r="T199" s="6"/>
-      <c r="U199" s="6"/>
-      <c r="V199" s="6"/>
-      <c r="W199" s="6"/>
-      <c r="X199" s="8"/>
-      <c r="Y199" s="6"/>
-      <c r="Z199" s="6"/>
-      <c r="AA199" s="8"/>
-      <c r="AB199" s="8"/>
-      <c r="AC199" s="8"/>
-      <c r="AD199" s="8"/>
-      <c r="AE199" s="6"/>
+      <c r="O199" s="5">
+        <v>2721.79</v>
+      </c>
+      <c r="P199" s="5">
+        <v>2721.79</v>
+      </c>
+      <c r="Q199" s="6">
+        <v>-0.52169412773614876</v>
+      </c>
+      <c r="R199" s="7">
+        <v>35</v>
+      </c>
+      <c r="S199" s="6">
+        <v>-0.453125</v>
+      </c>
+      <c r="T199" s="6">
+        <v>0.21579864721378211</v>
+      </c>
+      <c r="U199" s="6">
+        <v>-0.1641277982504161</v>
+      </c>
+      <c r="V199" s="6">
+        <v>0.02176545582135286</v>
+      </c>
+      <c r="W199" s="6">
+        <v>-0.01644836669985561</v>
+      </c>
+      <c r="X199" s="8">
+        <v>18.005553333333335</v>
+      </c>
+      <c r="Y199" s="6">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="Z199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA199" s="8">
+        <v>3.8300000000000005</v>
+      </c>
+      <c r="AB199" s="8">
+        <v>1.3933333333333333</v>
+      </c>
+      <c r="AC199" s="8">
+        <v>5.3566659999999997</v>
+      </c>
+      <c r="AD199" s="8">
+        <v>12.315553333333334</v>
+      </c>
+      <c r="AE199" s="6">
+        <v>1</v>
+      </c>
       <c r="AF199" s="9"/>
-      <c r="AG199" s="5"/>
+      <c r="AG199" s="5">
+        <v>-334.19999999999999</v>
+      </c>
       <c r="AH199" s="10">
         <v>1</v>
       </c>
@@ -26124,7 +27202,7 @@
         <v>19961</v>
       </c>
       <c r="B206" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C206" s="4">
         <v>44</v>
@@ -26160,25 +27238,57 @@
       <c t="s" r="N206" s="4">
         <v>52</v>
       </c>
-      <c r="O206" s="5"/>
-      <c r="P206" s="5"/>
+      <c r="O206" s="5">
+        <v>1361.46</v>
+      </c>
+      <c r="P206" s="5">
+        <v>1361.46</v>
+      </c>
       <c r="Q206" s="6"/>
-      <c r="R206" s="7"/>
+      <c r="R206" s="7">
+        <v>18</v>
+      </c>
       <c r="S206" s="6"/>
-      <c r="T206" s="6"/>
-      <c r="U206" s="6"/>
-      <c r="V206" s="6"/>
-      <c r="W206" s="6"/>
-      <c r="X206" s="8"/>
-      <c r="Y206" s="6"/>
-      <c r="Z206" s="6"/>
-      <c r="AA206" s="8"/>
-      <c r="AB206" s="8"/>
-      <c r="AC206" s="8"/>
-      <c r="AD206" s="8"/>
-      <c r="AE206" s="6"/>
+      <c r="T206" s="6">
+        <v>0.40980396045421824</v>
+      </c>
+      <c r="U206" s="6">
+        <v>0.011400775637918116</v>
+      </c>
+      <c r="V206" s="6">
+        <v>0.049933894495615</v>
+      </c>
+      <c r="W206" s="6">
+        <v>0.020898887958515123</v>
+      </c>
+      <c r="X206" s="8">
+        <v>24.06945</v>
+      </c>
+      <c r="Y206" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="Z206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA206" s="8">
+        <v>6.3470588235294123</v>
+      </c>
+      <c r="AB206" s="8">
+        <v>2.1916666666666669</v>
+      </c>
+      <c r="AC206" s="8">
+        <v>9.9055540000000004</v>
+      </c>
+      <c r="AD206" s="8">
+        <v>16.849999999999998</v>
+      </c>
+      <c r="AE206" s="6">
+        <v>0.83333333333333337</v>
+      </c>
       <c r="AF206" s="9"/>
-      <c r="AG206" s="5"/>
+      <c r="AG206" s="5">
+        <v>-258.89999999999998</v>
+      </c>
       <c r="AH206" s="10">
         <v>2</v>
       </c>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-22).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-22).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-170</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>R$ 903.004,18</t>
-  </si>
-  <si>
-    <t>R$ 4.988,97
-R$ 5.117,74</t>
-  </si>
-  <si>
-    <t>(9.4%)
-(7.0%)</t>
-  </si>
-  <si>
-    <t>52.6</t>
-  </si>
-  <si>
-    <t>(12.6%)</t>
-  </si>
-  <si>
-    <t>(267.0%)</t>
-  </si>
-  <si>
-    <t>(314.4%)</t>
+174</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>R$ 932.986,22</t>
+  </si>
+  <si>
+    <t>R$ 5.043,17
+R$ 5.172,40</t>
+  </si>
+  <si>
+    <t>(9.8%)
+(7.5%)</t>
+  </si>
+  <si>
+    <t>53.1</t>
+  </si>
+  <si>
+    <t>(13.1%)</t>
+  </si>
+  <si>
+    <t>(255.9%)</t>
+  </si>
+  <si>
+    <t>(303.0%)</t>
   </si>
   <si>
     <t>3.6%</t>
@@ -950,10 +950,10 @@
     <t>26.4</t>
   </si>
   <si>
-    <t>76.1%</t>
-  </si>
-  <si>
-    <t>8.2%</t>
+    <t>75.8%</t>
+  </si>
+  <si>
+    <t>8.4%</t>
   </si>
   <si>
     <t>5.3</t>
@@ -962,16 +962,16 @@
     <t>6.2</t>
   </si>
   <si>
-    <t>11.7</t>
+    <t>11.6</t>
   </si>
   <si>
     <t>18.2</t>
   </si>
   <si>
-    <t>74.1%</t>
-  </si>
-  <si>
-    <t>-R$ 28.231,75</t>
+    <t>73.9%</t>
+  </si>
+  <si>
+    <t>-R$ 31.527,23</t>
   </si>
   <si>
     <t>2.95</t>
@@ -2947,7 +2947,7 @@
         <v>19515</v>
       </c>
       <c r="B13" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C13" s="4">
         <v>44</v>
@@ -2983,25 +2983,61 @@
       <c t="s" r="N13" s="4">
         <v>52</v>
       </c>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="6"/>
-      <c r="R13" s="7"/>
-      <c r="S13" s="6"/>
-      <c r="T13" s="6"/>
-      <c r="U13" s="6"/>
-      <c r="V13" s="6"/>
-      <c r="W13" s="6"/>
-      <c r="X13" s="8"/>
-      <c r="Y13" s="6"/>
-      <c r="Z13" s="6"/>
-      <c r="AA13" s="8"/>
-      <c r="AB13" s="8"/>
-      <c r="AC13" s="8"/>
-      <c r="AD13" s="8"/>
-      <c r="AE13" s="6"/>
+      <c r="O13" s="5">
+        <v>10730.66</v>
+      </c>
+      <c r="P13" s="5">
+        <v>10730.66</v>
+      </c>
+      <c r="Q13" s="6">
+        <v>0.26790345621275846</v>
+      </c>
+      <c r="R13" s="7">
+        <v>104</v>
+      </c>
+      <c r="S13" s="6">
+        <v>0.11827956989247301</v>
+      </c>
+      <c r="T13" s="6">
+        <v>0.36397662399144137</v>
+      </c>
+      <c r="U13" s="6">
+        <v>0.0012673404990932524</v>
+      </c>
+      <c r="V13" s="6">
+        <v>0.025647005869163686</v>
+      </c>
+      <c r="W13" s="6">
+        <v>0.023778528068171018</v>
+      </c>
+      <c r="X13" s="8">
+        <v>30.826496153846154</v>
+      </c>
+      <c r="Y13" s="6">
+        <v>0.58974358974358976</v>
+      </c>
+      <c r="Z13" s="6">
+        <v>0.23076923076923078</v>
+      </c>
+      <c r="AA13" s="8">
+        <v>6.5258009615384616</v>
+      </c>
+      <c r="AB13" s="8">
+        <v>7.9318371794871796</v>
+      </c>
+      <c r="AC13" s="8">
+        <v>14.877940000000001</v>
+      </c>
+      <c r="AD13" s="8">
+        <v>21.740170512820516</v>
+      </c>
+      <c r="AE13" s="6">
+        <v>0.5</v>
+      </c>
       <c r="AF13" s="9"/>
-      <c r="AG13" s="5"/>
+      <c r="AG13" s="5">
+        <v>0</v>
+      </c>
       <c r="AH13" s="10">
         <v>5</v>
       </c>
@@ -5674,10 +5710,10 @@
         <v>-0.27049180327868849</v>
       </c>
       <c r="T34" s="6">
-        <v>0.31520344059011446</v>
+        <v>0.36659820691590961</v>
       </c>
       <c r="U34" s="6">
-        <v>-0.052905685870126284</v>
+        <v>-0.0015109195443311376</v>
       </c>
       <c r="V34" s="6">
         <v>0.070026974759332339</v>
@@ -6638,7 +6674,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>44</v>
@@ -6674,25 +6710,61 @@
       <c t="s" r="N42" s="4">
         <v>52</v>
       </c>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="6"/>
-      <c r="R42" s="7"/>
-      <c r="S42" s="6"/>
-      <c r="T42" s="6"/>
-      <c r="U42" s="6"/>
-      <c r="V42" s="6"/>
-      <c r="W42" s="6"/>
-      <c r="X42" s="8"/>
-      <c r="Y42" s="6"/>
-      <c r="Z42" s="6"/>
-      <c r="AA42" s="8"/>
-      <c r="AB42" s="8"/>
-      <c r="AC42" s="8"/>
-      <c r="AD42" s="8"/>
-      <c r="AE42" s="6"/>
+      <c r="O42" s="5">
+        <v>3256.8699999999999</v>
+      </c>
+      <c r="P42" s="5">
+        <v>3256.8699999999999</v>
+      </c>
+      <c r="Q42" s="6">
+        <v>-0.36057807462903413</v>
+      </c>
+      <c r="R42" s="7">
+        <v>35</v>
+      </c>
+      <c r="S42" s="6">
+        <v>-0.375</v>
+      </c>
+      <c r="T42" s="6">
+        <v>0.3731155373103624</v>
+      </c>
+      <c r="U42" s="6">
+        <v>0.065952524970293566</v>
+      </c>
+      <c r="V42" s="6">
+        <v>0.064620018606821886</v>
+      </c>
+      <c r="W42" s="6">
+        <v>0.0016915013494551519</v>
+      </c>
+      <c r="X42" s="8">
+        <v>25.575925925925926</v>
+      </c>
+      <c r="Y42" s="6">
+        <v>0.85185185185185186</v>
+      </c>
+      <c r="Z42" s="6">
+        <v>0.037037037037037035</v>
+      </c>
+      <c r="AA42" s="8">
+        <v>6.8720588235294118</v>
+      </c>
+      <c r="AB42" s="8">
+        <v>4.0969148148148147</v>
+      </c>
+      <c r="AC42" s="8">
+        <v>11.924073</v>
+      </c>
+      <c r="AD42" s="8">
+        <v>18.867285185185185</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>0.77777777777777779</v>
+      </c>
       <c r="AF42" s="9"/>
-      <c r="AG42" s="5"/>
+      <c r="AG42" s="5">
+        <v>-11.83</v>
+      </c>
       <c r="AH42" s="10">
         <v>3</v>
       </c>
@@ -7868,7 +7940,7 @@
         <v>19606</v>
       </c>
       <c r="B52" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C52" s="4">
         <v>44</v>
@@ -7904,25 +7976,61 @@
       <c t="s" r="N52" s="4">
         <v>52</v>
       </c>
-      <c r="O52" s="5"/>
-      <c r="P52" s="5"/>
-      <c r="Q52" s="6"/>
-      <c r="R52" s="7"/>
-      <c r="S52" s="6"/>
-      <c r="T52" s="6"/>
-      <c r="U52" s="6"/>
-      <c r="V52" s="6"/>
-      <c r="W52" s="6"/>
-      <c r="X52" s="8"/>
-      <c r="Y52" s="6"/>
-      <c r="Z52" s="6"/>
-      <c r="AA52" s="8"/>
-      <c r="AB52" s="8"/>
-      <c r="AC52" s="8"/>
-      <c r="AD52" s="8"/>
-      <c r="AE52" s="6"/>
+      <c r="O52" s="5">
+        <v>8431.1700000000001</v>
+      </c>
+      <c r="P52" s="5">
+        <v>8431.1700000000001</v>
+      </c>
+      <c r="Q52" s="6">
+        <v>-0.39873259294282759</v>
+      </c>
+      <c r="R52" s="7">
+        <v>71</v>
+      </c>
+      <c r="S52" s="6">
+        <v>-0.4580152671755725</v>
+      </c>
+      <c r="T52" s="6">
+        <v>0.089857042379646007</v>
+      </c>
+      <c r="U52" s="6">
+        <v>-0.27911547270426285</v>
+      </c>
+      <c r="V52" s="6">
+        <v>0.030041560068175592</v>
+      </c>
+      <c r="W52" s="6">
+        <v>0.016413558260597285</v>
+      </c>
+      <c r="X52" s="8">
+        <v>21.890197058823532</v>
+      </c>
+      <c r="Y52" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z52" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="8">
+        <v>4.2945945945945949</v>
+      </c>
+      <c r="AB52" s="8">
+        <v>1.4208343750000001</v>
+      </c>
+      <c r="AC52" s="8">
+        <v>6.0008330000000001</v>
+      </c>
+      <c r="AD52" s="8">
+        <v>13.491176470588234</v>
+      </c>
+      <c r="AE52" s="6">
+        <v>1</v>
+      </c>
       <c r="AF52" s="9"/>
-      <c r="AG52" s="5"/>
+      <c r="AG52" s="5">
+        <v>-2770.4499999999998</v>
+      </c>
       <c r="AH52" s="10">
         <v>1</v>
       </c>
@@ -8692,7 +8800,9 @@
       <c r="AB58" s="8">
         <v>4.1423076923076927</v>
       </c>
-      <c r="AC58" s="8"/>
+      <c r="AC58" s="8">
+        <v>7.1548069999999999</v>
+      </c>
       <c r="AD58" s="8">
         <v>14.096153846153847</v>
       </c>
@@ -10876,7 +10986,7 @@
         <v>19661</v>
       </c>
       <c r="B76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C76" s="4">
         <v>44</v>
@@ -10910,25 +11020,61 @@
       <c t="s" r="N76" s="4">
         <v>52</v>
       </c>
-      <c r="O76" s="5"/>
-      <c r="P76" s="5"/>
-      <c r="Q76" s="6"/>
-      <c r="R76" s="7"/>
-      <c r="S76" s="6"/>
-      <c r="T76" s="6"/>
-      <c r="U76" s="6"/>
-      <c r="V76" s="6"/>
-      <c r="W76" s="6"/>
-      <c r="X76" s="8"/>
-      <c r="Y76" s="6"/>
-      <c r="Z76" s="6"/>
-      <c r="AA76" s="8"/>
-      <c r="AB76" s="8"/>
-      <c r="AC76" s="8"/>
-      <c r="AD76" s="8"/>
-      <c r="AE76" s="6"/>
+      <c r="O76" s="5">
+        <v>7563.3400000000001</v>
+      </c>
+      <c r="P76" s="5">
+        <v>7563.3400000000001</v>
+      </c>
+      <c r="Q76" s="6">
+        <v>-0.22043737238495453</v>
+      </c>
+      <c r="R76" s="7">
+        <v>82</v>
+      </c>
+      <c r="S76" s="6">
+        <v>-0.27433628318584069</v>
+      </c>
+      <c r="T76" s="6">
+        <v>0.76830039374138936</v>
+      </c>
+      <c r="U76" s="6">
+        <v>0.35533072690107809</v>
+      </c>
+      <c r="V76" s="6">
+        <v>0.015757522470231405</v>
+      </c>
+      <c r="W76" s="6">
+        <v>-0.011349549273204695</v>
+      </c>
+      <c r="X76" s="8">
+        <v>28.982197727272727</v>
+      </c>
+      <c r="Y76" s="6">
+        <v>0.45454545454545453</v>
+      </c>
+      <c r="Z76" s="6">
+        <v>0.13636363636363635</v>
+      </c>
+      <c r="AA76" s="8">
+        <v>3.1172413793103448</v>
+      </c>
+      <c r="AB76" s="8">
+        <v>4.548147222222223</v>
+      </c>
+      <c r="AC76" s="8">
+        <v>7.6571749999999996</v>
+      </c>
+      <c r="AD76" s="8">
+        <v>15.382954545454545</v>
+      </c>
+      <c r="AE76" s="6">
+        <v>0.70454545454545459</v>
+      </c>
       <c r="AF76" s="9"/>
-      <c r="AG76" s="5"/>
+      <c r="AG76" s="5">
+        <v>-513.20000000000005</v>
+      </c>
       <c r="AH76" s="10">
         <v>2</v>
       </c>
@@ -16983,10 +17129,10 @@
         <v>0.095238095238095344</v>
       </c>
       <c r="T125" s="6">
-        <v>0.0027653903832646786</v>
+        <v>2.1430747546460642</v>
       </c>
       <c r="U125" s="6">
-        <v>-0.27968871846466337</v>
+        <v>1.8478318684864936</v>
       </c>
       <c r="V125" s="6">
         <v>0.066090567398773711</v>
@@ -20709,7 +20855,7 @@
         <v>0.022411290025424666</v>
       </c>
       <c r="W154" s="6">
-        <v>-0.019557831902428241</v>
+        <v>-0.020766424702457716</v>
       </c>
       <c r="X154" s="8">
         <v>20.169700000000002</v>
@@ -23867,7 +24013,9 @@
       <c r="AB179" s="8">
         <v>2.0033349999999999</v>
       </c>
-      <c r="AC179" s="8"/>
+      <c r="AC179" s="8">
+        <v>5.864166</v>
+      </c>
       <c r="AD179" s="8">
         <v>12.808335</v>
       </c>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-22).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-22).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-174</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>R$ 932.986,22</t>
-  </si>
-  <si>
-    <t>R$ 5.043,17
-R$ 5.172,40</t>
+181</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>R$ 964.194,34</t>
+  </si>
+  <si>
+    <t>R$ 5.021,85
+R$ 5.144,79</t>
   </si>
   <si>
     <t>(9.8%)
-(7.5%)</t>
-  </si>
-  <si>
-    <t>53.1</t>
-  </si>
-  <si>
-    <t>(13.1%)</t>
-  </si>
-  <si>
-    <t>(255.9%)</t>
-  </si>
-  <si>
-    <t>(303.0%)</t>
+(7.6%)</t>
+  </si>
+  <si>
+    <t>52.8</t>
+  </si>
+  <si>
+    <t>(13.0%)</t>
+  </si>
+  <si>
+    <t>(246.0%)</t>
+  </si>
+  <si>
+    <t>(292.7%)</t>
   </si>
   <si>
     <t>3.6%</t>
@@ -950,7 +950,7 @@
     <t>26.4</t>
   </si>
   <si>
-    <t>75.8%</t>
+    <t>76.0%</t>
   </si>
   <si>
     <t>8.4%</t>
@@ -962,7 +962,7 @@
     <t>6.2</t>
   </si>
   <si>
-    <t>11.6</t>
+    <t>11.5</t>
   </si>
   <si>
     <t>18.2</t>
@@ -971,10 +971,10 @@
     <t>73.9%</t>
   </si>
   <si>
-    <t>-R$ 31.527,23</t>
-  </si>
-  <si>
-    <t>2.95</t>
+    <t>-R$ 31.898,23</t>
+  </si>
+  <si>
+    <t>2.94</t>
   </si>
   <si>
     <t>3.52</t>
@@ -2066,7 +2066,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>44</v>
@@ -2102,25 +2102,61 @@
       <c t="s" r="N6" s="4">
         <v>52</v>
       </c>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="8"/>
-      <c r="AB6" s="8"/>
-      <c r="AC6" s="8"/>
-      <c r="AD6" s="8"/>
-      <c r="AE6" s="6"/>
+      <c r="O6" s="5">
+        <v>10065.09</v>
+      </c>
+      <c r="P6" s="5">
+        <v>10065.09</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>0.19701231252623819</v>
+      </c>
+      <c r="R6" s="7">
+        <v>104</v>
+      </c>
+      <c r="S6" s="6">
+        <v>0.28395061728395055</v>
+      </c>
+      <c r="T6" s="6">
+        <v>0.36426992704486494</v>
+      </c>
+      <c r="U6" s="6">
+        <v>0.0025533403079356469</v>
+      </c>
+      <c r="V6" s="6">
+        <v>0.041244261104470999</v>
+      </c>
+      <c r="W6" s="6">
+        <v>0.013697562565262705</v>
+      </c>
+      <c r="X6" s="8">
+        <v>20.258447945205479</v>
+      </c>
+      <c r="Y6" s="6">
+        <v>0.9452054794520548</v>
+      </c>
+      <c r="Z6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="8">
+        <v>5.4961670000000007</v>
+      </c>
+      <c r="AB6" s="8">
+        <v>1.4997680555555555</v>
+      </c>
+      <c r="AC6" s="8">
+        <v>7.106617</v>
+      </c>
+      <c r="AD6" s="8">
+        <v>14.028310958904111</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>1</v>
+      </c>
       <c r="AF6" s="9"/>
-      <c r="AG6" s="5"/>
+      <c r="AG6" s="5">
+        <v>0</v>
+      </c>
       <c r="AH6" s="10">
         <v>5</v>
       </c>
@@ -4388,7 +4424,7 @@
         <v>19536</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>44</v>
@@ -4424,25 +4460,59 @@
       <c t="s" r="N24" s="4">
         <v>52</v>
       </c>
-      <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="6"/>
-      <c r="R24" s="7"/>
-      <c r="S24" s="6"/>
-      <c r="T24" s="6"/>
-      <c r="U24" s="6"/>
-      <c r="V24" s="6"/>
-      <c r="W24" s="6"/>
-      <c r="X24" s="8"/>
-      <c r="Y24" s="6"/>
-      <c r="Z24" s="6"/>
-      <c r="AA24" s="8"/>
-      <c r="AB24" s="8"/>
+      <c r="O24" s="5">
+        <v>4579.8999999999996</v>
+      </c>
+      <c r="P24" s="5">
+        <v>4579.8999999999996</v>
+      </c>
+      <c r="Q24" s="6">
+        <v>-0.20137060351892866</v>
+      </c>
+      <c r="R24" s="7">
+        <v>55</v>
+      </c>
+      <c r="S24" s="6">
+        <v>-0.12698412698412698</v>
+      </c>
+      <c r="T24" s="6">
+        <v>3.1910358523111859</v>
+      </c>
+      <c r="U24" s="6">
+        <v>2.8363949212864914</v>
+      </c>
+      <c r="V24" s="6">
+        <v>0.030919889080547616</v>
+      </c>
+      <c r="W24" s="6">
+        <v>0.0046573069280988668</v>
+      </c>
+      <c r="X24" s="8">
+        <v>29.054274358974361</v>
+      </c>
+      <c r="Y24" s="6">
+        <v>0.84615384615384615</v>
+      </c>
+      <c r="Z24" s="6">
+        <v>0.10256410256410256</v>
+      </c>
+      <c r="AA24" s="8">
+        <v>3.2541673076923079</v>
+      </c>
+      <c r="AB24" s="8">
+        <v>11.461110256410256</v>
+      </c>
       <c r="AC24" s="8"/>
-      <c r="AD24" s="8"/>
-      <c r="AE24" s="6"/>
+      <c r="AD24" s="8">
+        <v>21.694443589743589</v>
+      </c>
+      <c r="AE24" s="6">
+        <v>0.61538461538461542</v>
+      </c>
       <c r="AF24" s="9"/>
-      <c r="AG24" s="5"/>
+      <c r="AG24" s="5">
+        <v>-217.19999999999999</v>
+      </c>
       <c r="AH24" s="10">
         <v>2</v>
       </c>
@@ -5710,10 +5780,10 @@
         <v>-0.27049180327868849</v>
       </c>
       <c r="T34" s="6">
-        <v>0.36659820691590961</v>
+        <v>0.40880480883363896</v>
       </c>
       <c r="U34" s="6">
-        <v>-0.0015109195443311376</v>
+        <v>0.040695682373398219</v>
       </c>
       <c r="V34" s="6">
         <v>0.070026974759332339</v>
@@ -5924,7 +5994,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>44</v>
@@ -5960,25 +6030,61 @@
       <c t="s" r="N36" s="4">
         <v>52</v>
       </c>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="8"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="8"/>
-      <c r="AB36" s="8"/>
-      <c r="AC36" s="8"/>
-      <c r="AD36" s="8"/>
-      <c r="AE36" s="6"/>
+      <c r="O36" s="5">
+        <v>4382.1599999999999</v>
+      </c>
+      <c r="P36" s="5">
+        <v>4382.1599999999999</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>0.048288400354041583</v>
+      </c>
+      <c r="R36" s="7">
+        <v>46</v>
+      </c>
+      <c r="S36" s="6">
+        <v>-0.021276595744680882</v>
+      </c>
+      <c r="T36" s="6">
+        <v>0.35339903152783103</v>
+      </c>
+      <c r="U36" s="6">
+        <v>0.017521290870255765</v>
+      </c>
+      <c r="V36" s="6">
+        <v>0.0519100169779287</v>
+      </c>
+      <c r="W36" s="6">
+        <v>0.0070736805593588558</v>
+      </c>
+      <c r="X36" s="8">
+        <v>29.165384615384614</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z36" s="6">
+        <v>0.19230769230769232</v>
+      </c>
+      <c r="AA36" s="8">
+        <v>5.8191489361702127</v>
+      </c>
+      <c r="AB36" s="8">
+        <v>7.2448730769230769</v>
+      </c>
+      <c r="AC36" s="8">
+        <v>13.458973</v>
+      </c>
+      <c r="AD36" s="8">
+        <v>20.405769230769231</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0.69230769230769229</v>
+      </c>
       <c r="AF36" s="9"/>
-      <c r="AG36" s="5"/>
+      <c r="AG36" s="5">
+        <v>-53.799999999999997</v>
+      </c>
       <c r="AH36" s="10">
         <v>4</v>
       </c>
@@ -7845,7 +7951,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7881,25 +7987,61 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
-      <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="O51" s="5">
+        <v>1516</v>
+      </c>
+      <c r="P51" s="5">
+        <v>1516</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>-0.24749329891789928</v>
+      </c>
+      <c r="R51" s="7">
+        <v>14</v>
+      </c>
+      <c r="S51" s="6">
+        <v>-0.17647058823529416</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.35099604221635883</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.024476912928759895</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.059962401055408975</v>
+      </c>
+      <c r="X51" s="8">
+        <v>16.856659999999998</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>2.9717923076923074</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>4.5533400000000004</v>
+      </c>
+      <c r="AC51" s="8">
+        <v>6.9766659999999998</v>
+      </c>
+      <c r="AD51" s="8">
+        <v>13.906659999999999</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>1</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -12604,7 +12746,7 @@
         <v>0</v>
       </c>
       <c r="AH88" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI88" s="11"/>
       <c r="AJ88" s="13">
@@ -12643,7 +12785,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>44</v>
@@ -12677,25 +12819,59 @@
       <c t="s" r="N89" s="4">
         <v>52</v>
       </c>
-      <c r="O89" s="5"/>
-      <c r="P89" s="5"/>
-      <c r="Q89" s="6"/>
-      <c r="R89" s="7"/>
-      <c r="S89" s="6"/>
-      <c r="T89" s="6"/>
-      <c r="U89" s="6"/>
-      <c r="V89" s="6"/>
-      <c r="W89" s="6"/>
-      <c r="X89" s="8"/>
-      <c r="Y89" s="6"/>
-      <c r="Z89" s="6"/>
-      <c r="AA89" s="8"/>
-      <c r="AB89" s="8"/>
+      <c r="O89" s="5">
+        <v>4725.5</v>
+      </c>
+      <c r="P89" s="5">
+        <v>4725.5</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>-0.26951163711013826</v>
+      </c>
+      <c r="R89" s="7">
+        <v>42</v>
+      </c>
+      <c r="S89" s="6">
+        <v>-0.39130434782608692</v>
+      </c>
+      <c r="T89" s="6">
+        <v>-1.3074375198391706</v>
+      </c>
+      <c r="U89" s="6">
+        <v>-1.6716931541635807</v>
+      </c>
+      <c r="V89" s="6">
+        <v>0.039832081261242193</v>
+      </c>
+      <c r="W89" s="6">
+        <v>0.017737064860861285</v>
+      </c>
+      <c r="X89" s="8">
+        <v>36.918181818181822</v>
+      </c>
+      <c r="Y89" s="6">
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="Z89" s="6">
+        <v>0.31818181818181818</v>
+      </c>
+      <c r="AA89" s="8">
+        <v>11.459756097560977</v>
+      </c>
+      <c r="AB89" s="8">
+        <v>7.8303045454545446</v>
+      </c>
       <c r="AC89" s="8"/>
-      <c r="AD89" s="8"/>
-      <c r="AE89" s="6"/>
+      <c r="AD89" s="8">
+        <v>27.259090909090911</v>
+      </c>
+      <c r="AE89" s="6">
+        <v>0.22727272727272727</v>
+      </c>
       <c r="AF89" s="9"/>
-      <c r="AG89" s="5"/>
+      <c r="AG89" s="5">
+        <v>-100</v>
+      </c>
       <c r="AH89" s="10">
         <v>2</v>
       </c>
@@ -14264,7 +14440,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>44</v>
@@ -14300,25 +14476,61 @@
       <c t="s" r="N102" s="4">
         <v>52</v>
       </c>
-      <c r="O102" s="5"/>
-      <c r="P102" s="5"/>
-      <c r="Q102" s="6"/>
-      <c r="R102" s="7"/>
-      <c r="S102" s="6"/>
-      <c r="T102" s="6"/>
-      <c r="U102" s="6"/>
-      <c r="V102" s="6"/>
-      <c r="W102" s="6"/>
-      <c r="X102" s="8"/>
-      <c r="Y102" s="6"/>
-      <c r="Z102" s="6"/>
-      <c r="AA102" s="8"/>
-      <c r="AB102" s="8"/>
-      <c r="AC102" s="8"/>
-      <c r="AD102" s="8"/>
-      <c r="AE102" s="6"/>
+      <c r="O102" s="5">
+        <v>3445.54</v>
+      </c>
+      <c r="P102" s="5">
+        <v>3445.54</v>
+      </c>
+      <c r="Q102" s="6">
+        <v>-0.18771747842896891</v>
+      </c>
+      <c r="R102" s="7">
+        <v>36</v>
+      </c>
+      <c r="S102" s="6">
+        <v>-0.28000000000000003</v>
+      </c>
+      <c r="T102" s="6">
+        <v>0.17729577947143263</v>
+      </c>
+      <c r="U102" s="6">
+        <v>-0.18685033405503926</v>
+      </c>
+      <c r="V102" s="6">
+        <v>0.017436454082669191</v>
+      </c>
+      <c r="W102" s="6">
+        <v>-0.0072186072429865859</v>
+      </c>
+      <c r="X102" s="8">
+        <v>29.838000000000001</v>
+      </c>
+      <c r="Y102" s="6">
+        <v>0.11538461538461539</v>
+      </c>
+      <c r="Z102" s="6">
+        <v>0.12</v>
+      </c>
+      <c r="AA102" s="8">
+        <v>6.4912289473684206</v>
+      </c>
+      <c r="AB102" s="8">
+        <v>9.6150000000000002</v>
+      </c>
+      <c r="AC102" s="8">
+        <v>16.072141999999999</v>
+      </c>
+      <c r="AD102" s="8">
+        <v>20.538</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>0.52000000000000002</v>
+      </c>
       <c r="AF102" s="9"/>
-      <c r="AG102" s="5"/>
+      <c r="AG102" s="5">
+        <v>0</v>
+      </c>
       <c r="AH102" s="10">
         <v>2</v>
       </c>
@@ -16645,7 +16857,7 @@
         <v>0</v>
       </c>
       <c r="AH121" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI121" s="11"/>
       <c r="AJ121" s="13">
@@ -18608,7 +18820,7 @@
         <v>-287.69999999999999</v>
       </c>
       <c r="AH136" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI136" s="11"/>
       <c r="AJ136" s="13">
@@ -20886,7 +21098,7 @@
         <v>-46.799999999999997</v>
       </c>
       <c r="AH154" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI154" s="11"/>
       <c r="AJ154" s="13">
@@ -21280,7 +21492,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>44</v>
@@ -21316,25 +21528,61 @@
       <c t="s" r="N158" s="4">
         <v>52</v>
       </c>
-      <c r="O158" s="5"/>
-      <c r="P158" s="5"/>
-      <c r="Q158" s="6"/>
-      <c r="R158" s="7"/>
-      <c r="S158" s="6"/>
-      <c r="T158" s="6"/>
-      <c r="U158" s="6"/>
-      <c r="V158" s="6"/>
-      <c r="W158" s="6"/>
-      <c r="X158" s="8"/>
-      <c r="Y158" s="6"/>
-      <c r="Z158" s="6"/>
-      <c r="AA158" s="8"/>
-      <c r="AB158" s="8"/>
-      <c r="AC158" s="8"/>
-      <c r="AD158" s="8"/>
-      <c r="AE158" s="6"/>
+      <c r="O158" s="5">
+        <v>2493.9299999999998</v>
+      </c>
+      <c r="P158" s="5">
+        <v>2493.9299999999998</v>
+      </c>
+      <c r="Q158" s="6">
+        <v>-0.32395866652932215</v>
+      </c>
+      <c r="R158" s="7">
+        <v>28</v>
+      </c>
+      <c r="S158" s="6">
+        <v>-0.28205128205128205</v>
+      </c>
+      <c r="T158" s="6">
+        <v>0.34971831607142145</v>
+      </c>
+      <c r="U158" s="6">
+        <v>0.0030125143849266019</v>
+      </c>
+      <c r="V158" s="6">
+        <v>0.039479656606239956</v>
+      </c>
+      <c r="W158" s="6">
+        <v>-0.0094511473858528514</v>
+      </c>
+      <c r="X158" s="8">
+        <v>25.088335000000001</v>
+      </c>
+      <c r="Y158" s="6">
+        <v>0.80000000000000004</v>
+      </c>
+      <c r="Z158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA158" s="8">
+        <v>5.681481481481482</v>
+      </c>
+      <c r="AB158" s="8">
+        <v>2.2949999999999999</v>
+      </c>
+      <c r="AC158" s="8">
+        <v>8.3408329999999999</v>
+      </c>
+      <c r="AD158" s="8">
+        <v>15.291665</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>0.90000000000000002</v>
+      </c>
       <c r="AF158" s="9"/>
-      <c r="AG158" s="5"/>
+      <c r="AG158" s="5">
+        <v>0</v>
+      </c>
       <c r="AH158" s="10">
         <v>2</v>
       </c>
@@ -26069,7 +26317,9 @@
       <c r="AB195" s="8">
         <v>6.0012807692307693</v>
       </c>
-      <c r="AC195" s="8"/>
+      <c r="AC195" s="8">
+        <v>10.202564000000001</v>
+      </c>
       <c r="AD195" s="8">
         <v>17.139742307692309</v>
       </c>
